--- a/docs/xlsx/jobs-2026-10-06.xlsx
+++ b/docs/xlsx/jobs-2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="609">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,1035 @@
     <t>Link</t>
   </si>
   <si>
+    <t>AmeriCorps Conservation Educator at Teton Raptor Center</t>
+  </si>
+  <si>
+    <t>Teton Raptor Center</t>
+  </si>
+  <si>
+    <t>Jackson, WY</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>Living allowance of $400 per week during the term of service</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-conservation-educator-at-teton-raptor-center-jackson-wyoming/6202650704</t>
+  </si>
+  <si>
+    <t>AmeriCorps Crew Leader</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Conservancy</t>
+  </si>
+  <si>
+    <t>Estes Park, CO</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-crew-leader-estes-park-colorado/4189607019</t>
+  </si>
+  <si>
+    <t>AmeriCorps Crew Member</t>
+  </si>
+  <si>
+    <t>$500 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-crew-member-estes-park-colorado/6995450239</t>
+  </si>
+  <si>
+    <t>Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>Southern Appalachian Wilderness Stewards (SAWS)</t>
+  </si>
+  <si>
+    <t>Roanoke, VA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$23 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-crew-leader-roanoke-virginia/5789364719</t>
+  </si>
+  <si>
+    <t>Associate Engineer - Environmental Services Department, Water Resources Division</t>
+  </si>
+  <si>
+    <t>City of San Jose Environmental Services Department</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>$135,975.84 - $172,099.20 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-engineer---environmental-services-department-water-resources-division-san-jose-california/3161990096</t>
+  </si>
+  <si>
+    <t>Community Conservation Senior Manager</t>
+  </si>
+  <si>
+    <t>Panthera</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Salary is competitive with experience.</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-conservation-senior-manager-new-york-new-york/8720897735</t>
+  </si>
+  <si>
+    <t>Conservation Corps - Field Coordinator</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$1,057.69 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps---field-coordinator-estes-park-colorado/4240138765</t>
+  </si>
+  <si>
+    <t>Conservation Educator Internship</t>
+  </si>
+  <si>
+    <t>Hanover-Caroline Soil and Water Conservation District</t>
+  </si>
+  <si>
+    <t>Hanover, VA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-educator-internship-hanover-virginia/7191861588</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Vermont Mountain Bike Association</t>
+  </si>
+  <si>
+    <t>Waterbury, VT</t>
+  </si>
+  <si>
+    <t>$75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-director-waterbury-vermont/8438071578</t>
+  </si>
+  <si>
+    <t>Easement Program Stewardship Specialist</t>
+  </si>
+  <si>
+    <t>Watershed Agricultural Council</t>
+  </si>
+  <si>
+    <t>Walton, NY</t>
+  </si>
+  <si>
+    <t>$55,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-easement-program-stewardship-specialist-walton-new-york/3591176931</t>
+  </si>
+  <si>
+    <t>Fish Screening, Passage and Restoration Coordinator (Natural Resource Specialist 2)</t>
+  </si>
+  <si>
+    <t>Oregon Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Klamath Falls, OR</t>
+  </si>
+  <si>
+    <t>$4,738 - $7,247 per month</t>
+  </si>
+  <si>
+    <t>fisheries-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-screening-passage-and-restoration-coordinator-natural-resource-specialist-2-klamath-falls-oregon/3206718583</t>
+  </si>
+  <si>
+    <t>Forester/Entry level Forester</t>
+  </si>
+  <si>
+    <t>DelAtlantic Conservation District</t>
+  </si>
+  <si>
+    <t>West Berlin, NJ</t>
+  </si>
+  <si>
+    <t>Commensurate w/experience</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-foresterentry-level-forester-west-berlin-new-jersey/5009348714</t>
+  </si>
+  <si>
+    <t>Lakes Region Conservation Corps Member- Various Locations</t>
+  </si>
+  <si>
+    <t>Lakes Region Conservation Corps</t>
+  </si>
+  <si>
+    <t>Holderness, NH</t>
+  </si>
+  <si>
+    <t>$20,400 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lakes-region-conservation-corps-member--various-locations-holderness-new-hampshire/1671166632</t>
+  </si>
+  <si>
+    <t>Land Use Planner</t>
+  </si>
+  <si>
+    <t>Mountain Area Preservation</t>
+  </si>
+  <si>
+    <t>Truckee, CA</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-use-planner-truckee-california/9041601700</t>
+  </si>
+  <si>
+    <t>Maryland Coastal Fellowship</t>
+  </si>
+  <si>
+    <t>Maryland Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Annapolis, MD</t>
+  </si>
+  <si>
+    <t>$55,000 per year</t>
+  </si>
+  <si>
+    <t>restoration-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maryland-coastal-fellowship-annapolis-maryland/2080475315</t>
+  </si>
+  <si>
+    <t>Nursery Manager</t>
+  </si>
+  <si>
+    <t>Cannabis for Conservation</t>
+  </si>
+  <si>
+    <t>Mckinleyville, CA</t>
+  </si>
+  <si>
+    <t>$38 - $45 per hour</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nursery-manager-mckinleyville-california/4427837536</t>
+  </si>
+  <si>
+    <t>Outdoor Program Instructor</t>
+  </si>
+  <si>
+    <t>Sierra Nevada Journeys</t>
+  </si>
+  <si>
+    <t>Portola, CA</t>
+  </si>
+  <si>
+    <t>$118.32 - $123.32 per day</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-program-instructor-portola-california/6651825507</t>
+  </si>
+  <si>
+    <t>Research &amp; Planning Coordinator, Stream Management Program</t>
+  </si>
+  <si>
+    <t>City of New York, Dept. of Environmental Protection, Bureau of Water Supply</t>
+  </si>
+  <si>
+    <t>Arkville, NY</t>
+  </si>
+  <si>
+    <t>$98,159 per year</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research--planning-coordinator-stream-management-program-arkville-new-york/1438195099</t>
+  </si>
+  <si>
+    <t>Resource Specialist II</t>
+  </si>
+  <si>
+    <t>Cascadia Conservation District</t>
+  </si>
+  <si>
+    <t>Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>$31.62 - $40.35 per hour</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-specialist-ii-wenatchee-washington/9802853800</t>
+  </si>
+  <si>
+    <t>Scientist, Water Ecologist</t>
+  </si>
+  <si>
+    <t>Valhalla, NY</t>
+  </si>
+  <si>
+    <t>$76,554 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-scientist-water-ecologist-valhalla-new-york/4961414344</t>
+  </si>
+  <si>
+    <t>Seasonal Membership Sales Assistant</t>
+  </si>
+  <si>
+    <t>National Audubon Society</t>
+  </si>
+  <si>
+    <t>Naples, FL</t>
+  </si>
+  <si>
+    <t>$19 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-membership-sales-assistant-naples-florida/5040491360</t>
+  </si>
+  <si>
+    <t>Senior Communications Manager, Ending Ocean Plastics</t>
+  </si>
+  <si>
+    <t>Ocean Conservancy</t>
+  </si>
+  <si>
+    <t>AK, CA, DC (preferred), FL, MD, OR, VA, TX, WA, or WV, DC</t>
+  </si>
+  <si>
+    <t>$90,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-enior-communications-manager-ending-ocean-plastics-ak-ca-dc-preferred-fl-md-or-va-tx-wa-or-wv-dc/7990595979</t>
+  </si>
+  <si>
+    <t>Senior Wildlife Technician - Habitat</t>
+  </si>
+  <si>
+    <t>Idaho Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$22.66 - $28.33 per hour</t>
+  </si>
+  <si>
+    <t>restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-wildlife-technician---habitat-boise-idaho/8542441370</t>
+  </si>
+  <si>
+    <t>Social Media Coordinator</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>United States, Remote</t>
+  </si>
+  <si>
+    <t>$65,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-social-media-coordinator-united-states-remote/3431263209</t>
+  </si>
+  <si>
+    <t>Social Services Aid (YCC) Seasonal</t>
+  </si>
+  <si>
+    <t>Yellowstone NP YCC</t>
+  </si>
+  <si>
+    <t>Mammoth Hot Spring, WY</t>
+  </si>
+  <si>
+    <t>$17.88 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-social-services-aid-ycc-seasonal-mammoth-hot-springsq-wyoming/3887056368</t>
+  </si>
+  <si>
+    <t>Supervisor, Enforcement (Natural Areas Lead Ranger) (Full-Time Regular) (Classified)</t>
+  </si>
+  <si>
+    <t>City of Fort Collins Natural Areas</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO</t>
+  </si>
+  <si>
+    <t>$71,000 - $78,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-supervisor-enforcement-natural-areas-lead-ranger---full-time-regular-classified-fort-collins-colorado/8402628922</t>
+  </si>
+  <si>
+    <t>Water Quality Monitoring Specialist</t>
+  </si>
+  <si>
+    <t>Neponset River Watershed Association</t>
+  </si>
+  <si>
+    <t>Canton, MA</t>
+  </si>
+  <si>
+    <t>$55,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-quality-monitoring-specialist-canton-massachusetts/7035132310</t>
+  </si>
+  <si>
+    <t>Watershed Forester</t>
+  </si>
+  <si>
+    <t>Kingston, NY</t>
+  </si>
+  <si>
+    <t>$78,740 per year</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-forester-kingston-new-york/1279981805</t>
+  </si>
+  <si>
+    <t>Wild Turkey Technician</t>
+  </si>
+  <si>
+    <t>University of Rhode Island</t>
+  </si>
+  <si>
+    <t>Kingston, RI</t>
+  </si>
+  <si>
+    <t>$2,500 - $3,000 per month</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wild-turkey-technician-kingston-rhode-island/8559793490</t>
+  </si>
+  <si>
+    <t>Wildlife Management Specialist</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Russell, IA</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-management-specialist-russell-iowa/5731570632</t>
+  </si>
+  <si>
+    <t>Wyss Fellow Term-limited</t>
+  </si>
+  <si>
+    <t>Grand Staircase Escalante Partners</t>
+  </si>
+  <si>
+    <t>Cedar City, UT</t>
+  </si>
+  <si>
+    <t>$68,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wyss-fellow-term-limited-cedar-city-utah/4125763179</t>
+  </si>
+  <si>
+    <t>YCC Crew Leader</t>
+  </si>
+  <si>
+    <t>Yellowstone NP</t>
+  </si>
+  <si>
+    <t>Yellowstone, WY</t>
+  </si>
+  <si>
+    <t>$19.52 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ycc-crew-leader-yellowstone-wyoming/3666454332</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Southeastern Wind Coalition</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/program-manager-11/</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Sage Steppe Wild</t>
+  </si>
+  <si>
+    <t>40,000 - 60,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/staff-attorney-7/</t>
+  </si>
+  <si>
+    <t>Afterschool Coordinator (Castle Hill YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75276a6526a8429e93cbd71a2e201671-afterschool-coordinator-castle-hill-ymca-ymca-of-greater-new-york-bronx</t>
+  </si>
+  <si>
+    <t>Asistente de Redes Sociales Remoto/a</t>
+  </si>
+  <si>
+    <t>Clínica Virtual - Especializada en salud mental</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/755c3d95234f4b1e97a9bea9935ad7cc-asistente-de-redes-sociales-remotoa-clinica-virtual-especializada-en-salud-mental-buenos-aires</t>
+  </si>
+  <si>
+    <t>Asset Manager, ROC USA Capital</t>
+  </si>
+  <si>
+    <t>ROC USA</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cab186eeed14ed2a22da2b8d7b942ff-asset-manager-roc-usa-capital-roc-usa-washington</t>
+  </si>
+  <si>
+    <t>Associate Director of Admissions</t>
+  </si>
+  <si>
+    <t>Institute for Nonprofit Practice</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4bacc7bef85e4296b0a41d1c2096ff7b-associate-director-of-admissions-institute-for-nonprofit-practice-boston</t>
+  </si>
+  <si>
+    <t>Associate Director of Philanthropy</t>
+  </si>
+  <si>
+    <t>Spirit Juice Entertainment Group</t>
+  </si>
+  <si>
+    <t>Alsip, Illinois</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0ebd1697cac4f99a3011bbff60e0df0-associate-director-of-philanthropy-spirit-juice-entertainment-group-alsip</t>
+  </si>
+  <si>
+    <t>Associate Director, Foundation Giving</t>
+  </si>
+  <si>
+    <t>True Ground Housing Partners</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 117000.00 - 156000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4890b74e7a3343fca168d3c4e07fdb53-associate-director-foundation-giving-true-ground-housing-partners-arlington</t>
+  </si>
+  <si>
+    <t>Chief Conservation Officer</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 280000.00 - 350000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5e0b9c13c4e54d958d36956e74f9a8f5-chief-conservation-officer-ocean-conservancy-washington</t>
+  </si>
+  <si>
+    <t>Chief Program Officer, Exoneration Strategy &amp; Support</t>
+  </si>
+  <si>
+    <t>Innocence Project</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 229500.00 - 298000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5ed5359f03248ca8a8fb1b39a0ac35d-chief-program-officer-exoneration-strategy-support-innocence-project-new-york</t>
+  </si>
+  <si>
+    <t>Communications Manager, Start Early WA</t>
+  </si>
+  <si>
+    <t>Start Early</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 73900.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aaf8af60b41c4713bd046cf1c415396f-communications-manager-start-early-wa-start-early-chicago</t>
+  </si>
+  <si>
+    <t>Community Organizer, Hunts Point Community Partnership</t>
+  </si>
+  <si>
+    <t>Hunts Point Alliance for Children</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Urban Areas, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dfd232c157e4f51bfd29a92b7efc15c-community-organizer-hunts-point-community-partnership-hunts-point-alliance-for-children-bronx</t>
+  </si>
+  <si>
+    <t>Conference &amp; Events Associate</t>
+  </si>
+  <si>
+    <t>The Democracy Alliance</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b825e229c09643c09119f16e77531aa1-conference-events-associate-the-democracy-alliance-washington</t>
+  </si>
+  <si>
+    <t>CRM/ERP Administrator</t>
+  </si>
+  <si>
+    <t>Metropolitan Council on Jewish Poverty</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f68d65ab16a42018f4db4929b914c20-crmerp-administrator-metropolitan-council-on-jewish-poverty-new-york</t>
+  </si>
+  <si>
+    <t>CSHE Executive Assistant</t>
+  </si>
+  <si>
+    <t>Community Solutions for Health Equity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b179abce87c4a1dbeaa3c0dabb95131-cshe-executive-assistant-community-solutions-for-health-equity-boston</t>
+  </si>
+  <si>
+    <t>Deputy Director, Strategy &amp; Operations</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy</t>
+  </si>
+  <si>
+    <t>Conshohocken, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 112000.00 - 137000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/793da77ec69f4f5f9f63a6be9ea2cc44-deputy-director-strategy-operations-the-nature-conservancy-conshohocken</t>
+  </si>
+  <si>
+    <t>Whatcom Hills Waldorf School</t>
+  </si>
+  <si>
+    <t>Bellingham, Washington</t>
+  </si>
+  <si>
+    <t>USD 76900.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dea8746676104822a233e97505b880ec-development-director-whatcom-hills-waldorf-school-bellingham</t>
+  </si>
+  <si>
+    <t>Development Manager, Start Early WA</t>
+  </si>
+  <si>
+    <t>USD 77400.00 - 87720.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3afba97967ec438e8e3634733ac8be42-development-manager-start-early-wa-start-early-chicago</t>
+  </si>
+  <si>
+    <t>Development Operations &amp; Annual Giving Manager</t>
+  </si>
+  <si>
+    <t>Gorilla Doctors (MGVP, Inc.)</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1ff885640cc43be845704035c75c919-development-operations-annual-giving-manager-gorilla-doctors-mgvp-inc-davis</t>
+  </si>
+  <si>
+    <t>Digital Coordinator - Part-Time</t>
+  </si>
+  <si>
+    <t>United Today, Stronger Tomorrow</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25d4074acb2546c1b30439b2d6155167-digital-coordinator-part-time-united-today-stronger-tomorrow-salt-lake-city</t>
+  </si>
+  <si>
+    <t>Digital Media Specialist (Part-time preferred)</t>
+  </si>
+  <si>
+    <t>Galveston-Houston Immigrant Representation Project</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19af048780dd41c6be883885b6e634e4-digital-media-specialist-part-time-preferred-galveston-houston-immigrant-representation-project-houston</t>
+  </si>
+  <si>
+    <t>Director of Brand and Communications</t>
+  </si>
+  <si>
+    <t>Foodbank of Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Goleta, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/120d922a5c284efc9de01958cb1b3493-director-of-brand-and-communications-foodbank-of-santa-barbara-county-goleta</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Pittsburgh Life Sciences Alliance</t>
+  </si>
+  <si>
+    <t>Pittsburgh, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Science Technology, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef2d0d524b4e4f6fa472514d16794101-director-of-finance-pittsburgh-life-sciences-alliance-pittsburgh</t>
+  </si>
+  <si>
+    <t>Director of Information Technology</t>
+  </si>
+  <si>
+    <t>Project On Government Oversight</t>
+  </si>
+  <si>
+    <t>USD 128000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65b0226ad4ba41d181dafd64282b5f98-director-of-information-technology-project-on-government-oversight-washington</t>
+  </si>
+  <si>
+    <t>Director of Jacj Cuisi Wildlife Sanctuary</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>San Buena Ventura, La Paz, Bolivia, Departamento de La Paz, BO</t>
+  </si>
+  <si>
+    <t>USD 400.00 - 450.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c2088e7445542dab32a916256b08d46-director-of-jacj-cuisi-wildlife-sanctuary-comunidad-inti-wara-yassi-ciwy-san-buena-ventura-la-paz-bolivia</t>
+  </si>
+  <si>
+    <t>Director of Policy and Government Affairs</t>
+  </si>
+  <si>
+    <t>Advocates for Community Health, Inc.</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/310b7118d63148f5b5f7102bc2976dc8-director-of-policy-and-government-affairs-advocates-for-community-health-inc-washington</t>
+  </si>
+  <si>
+    <t>Director of Program Admissions &amp; Impact</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df931260942d408a8c00ec1911ae008b-director-of-program-admissions-impact-institute-for-nonprofit-practice-boston</t>
+  </si>
+  <si>
+    <t>Director, Corporate and Foundation Relations</t>
+  </si>
+  <si>
+    <t>Spoonfuls</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/507a125cc65841769ae79a6ebd033fa5-director-corporate-and-foundation-relations-spoonfuls-newton</t>
+  </si>
+  <si>
+    <t>Director/a del Santuario Jacj Cuisi</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b93b38b635d14dbfac6f9abc6aac1a89-directora-del-santuario-jacj-cuisi-comunidad-inti-wara-yassi-ciwy-san-buena-ventura-la-paz-bolivia</t>
+  </si>
+  <si>
+    <t>Donor Engagement Officer</t>
+  </si>
+  <si>
+    <t>Triangle Community Foundation</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Children Youth, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/118f68f787f641d39c497287a8ca274a-donor-engagement-officer-triangle-community-foundation-durham</t>
+  </si>
+  <si>
+    <t>Employee Benefits Specialist</t>
+  </si>
+  <si>
+    <t>SEEC</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 51500.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7255f06f709450bb26035b87afd8767-employee-benefits-specialist-seec-silver-spring</t>
+  </si>
+  <si>
     <t>ET Secretary + Admin</t>
   </si>
   <si>
@@ -49,18 +1078,165 @@
     <t>Chennai, Tamil Nadu, IN</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Economic Development, Community Development, Entrepreneurship</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9214c5ebbfeb477db09726786618dd20-et-secretary-admin-empower-tamizhagam-chennai</t>
   </si>
   <si>
+    <t>ET Secretary + Admin [Chennai]</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9214c5ebbfeb477db09726786618dd20-et-secretary-admin-chennai-empower-tamizhagam-chennai</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Center for Improving Youth Justice</t>
+  </si>
+  <si>
+    <t>Braintree, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a3228da41a94f27b308a024f6764196-executive-assistant-center-for-improving-youth-justice-braintree</t>
+  </si>
+  <si>
+    <t>Executive Assistant &amp; Office Manager</t>
+  </si>
+  <si>
+    <t>Merrimack Valley Housing Partnership</t>
+  </si>
+  <si>
+    <t>Lowell, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12df9fc2acc840dd98825d50feb56a96-executive-assistant-office-manager-merrimack-valley-housing-partnership-lowell</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Newark Day Nursery and Children’s Center</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/153986d04b934e6ca9afb34f5c5d67c4-executive-director-newark-day-nursery-and-childrens-center-newark</t>
+  </si>
+  <si>
+    <t>LWVFL-League of Women Voters of Florida</t>
+  </si>
+  <si>
+    <t>Remote (Florida)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c41cb7f06d5463685ca4e5fb336b8ea-executive-director-lwvfl-league-of-women-voters-of-florida-orlando</t>
+  </si>
+  <si>
+    <t>Executive Director, Cambridge Center for Adult Education</t>
+  </si>
+  <si>
+    <t>The Cambridge Center for Adult Education</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8330b0a62ca476ca56cd9bf3496ac8e-executive-director-cambridge-center-for-adult-education-the-cambridge-center-for-adult-education-cambridge</t>
+  </si>
+  <si>
+    <t>Facilities Director</t>
+  </si>
+  <si>
+    <t>Lexington Housing Assistance Board, Inc</t>
+  </si>
+  <si>
+    <t>Lexington, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41282582321a477e802a1ad6a4b85b8f-facilities-director-lexington-housing-assistance-board-inc-lexington</t>
+  </si>
+  <si>
+    <t>Finance Director</t>
+  </si>
+  <si>
+    <t>Trees, Water &amp; People</t>
+  </si>
+  <si>
+    <t>Fort Collins, Colorado</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a0a1b527cf44203a06cc166d6e8d899-finance-director-trees-water-people-fort-collins</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Flatbush Cats</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72d8f47d46f54c9c8768cfa21d26890c-finance-manager-flatbush-cats-kings-county</t>
+  </si>
+  <si>
+    <t>Financial Coach and Educator</t>
+  </si>
+  <si>
+    <t>Just A Start</t>
+  </si>
+  <si>
+    <t>USD 56550.00 - 66300.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a75ef395a4747e6925b263ce94deb27-financial-coach-and-educator-just-a-start-cambridge</t>
+  </si>
+  <si>
     <t>Head of Project Sudan</t>
   </si>
   <si>
@@ -79,27 +1255,408 @@
     <t>https://www.idealist.org/en/nonprofit-job/37b3b90da14f4857b148a2d5aa8f7164-head-of-project-sudan-welthungerhilfe-kassala</t>
   </si>
   <si>
+    <t>Head Start Teacher - JJ Flynn Elementary</t>
+  </si>
+  <si>
+    <t>Champlain Valley Office of Economic Opportunity</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 23.73 - 28.76/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54b3c2246ae149e58dcd0ae6b5dcaefa-head-start-teacher-jj-flynn-elementary-champlain-valley-office-of-economic-opportunity-burlington</t>
+  </si>
+  <si>
+    <t>IMMIGRATION LAW ATTORNEY CWJC (Springfield)</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b13e854d3684d22bc8bd4a3f509b60c-immigration-law-attorney-cwjc-springfield-community-legal-aid-affiliate-springfield</t>
+  </si>
+  <si>
+    <t>In-Home Support Worker</t>
+  </si>
+  <si>
+    <t>HopeWell Inc.</t>
+  </si>
+  <si>
+    <t>Dedham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 57500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3c94ed05d0f444bab83b87532299147-in-home-support-worker-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Internal Communications Manager</t>
+  </si>
+  <si>
+    <t>Meliore Foundation</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c01f20d4f4584cfb8351537e84baf210-internal-communications-manager-meliore-foundation-bruxelles</t>
+  </si>
+  <si>
+    <t>IT &amp; Office Associate</t>
+  </si>
+  <si>
+    <t>Writopia Lab</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc947aa95a99421fa228fc523067b28e-it-office-associate-writopia-lab-new-york</t>
+  </si>
+  <si>
+    <t>Licensed Clinician-Worcester</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecbe515278784045afb955d3a666234a-licensed-clinician-worcester-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Líder de Desarrollo de Mercado y Escalabilidad – Biológicos para el agro</t>
+  </si>
+  <si>
+    <t>Por el Mar</t>
+  </si>
+  <si>
+    <t>San Isidro, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>ARS 4500000.00/month</t>
+  </si>
+  <si>
+    <t>Environment, Agriculture, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a33c287e9184c51b4d8a50acd22f548-lider-de-desarrollo-de-mercado-y-escalabilidad-biologicos-para-el-agro-por-el-mar-san-isidro</t>
+  </si>
+  <si>
+    <t>Lifeguard</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e62c3a015194b3ba933d725f5cb7e3a-lifeguard-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Literacy Interventionist, Full Time</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 66250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77bd43fcc82e426d952f5df4451301c7-literacy-interventionist-full-time-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Literacy Interventionist, Part Time</t>
+  </si>
+  <si>
+    <t>USD 27.47 - 36.40/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e66fd76111e4397a329456698d32e80-literacy-interventionist-part-time-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Local Food Access Delivery Driver</t>
+  </si>
+  <si>
+    <t>The People's Market</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 80.00 - 125.00/day</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/65a0b15d1dce45b0b382cbcec47b2439-local-food-access-delivery-driver-the-peoples-market-hyattsville</t>
+  </si>
+  <si>
+    <t>Manager, Office of the President</t>
+  </si>
+  <si>
+    <t>United Way of Central and Northeastern CT</t>
+  </si>
+  <si>
+    <t>Hartford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52eb4b7f87ce4a9f912678de5a2dc54f-manager-office-of-the-president-united-way-of-central-and-northeastern-ct-hartford</t>
+  </si>
+  <si>
+    <t>Middle School Science Teacher</t>
+  </si>
+  <si>
+    <t>Two Rivers Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 66173.00 - 106668.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72f0b46752a34e51a0d5e7a8846623ea-middle-school-science-teacher-two-rivers-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>National Echelon Manager</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 67496.00 - 87657.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1603aa5c2ead471786f5fdfb694ca6fc-national-echelon-manager-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>NSLP Operations Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ea097974a8d41b78dd6fb71072a7e75-nslp-operations-manager-metropolitan-council-on-jewish-poverty-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>Lambda Legal</t>
+  </si>
+  <si>
+    <t>USD 59053.00 - 86723.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad22e8c3e1f441568c45890feb1e3da1-paralegal-lambda-legal-new-york</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>The Breast Cancer Research Foundation</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc1369ed198b4b6196a04384d5b55376-philanthropy-officer-the-breast-cancer-research-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Post-Conviction Litigation Fellow</t>
+  </si>
+  <si>
+    <t>USD 93000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6ddb3497f11463688baa52e4305f206-post-conviction-litigation-fellow-innocence-project-new-york</t>
+  </si>
+  <si>
+    <t>ProBAR Legal Services - Senior Staff Attorney TX-CA</t>
+  </si>
+  <si>
+    <t>American Bar Association</t>
+  </si>
+  <si>
+    <t>Harlingen, Texas</t>
+  </si>
+  <si>
+    <t>USD 79730.00 - 95516.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38b8b3a35ce8440cb40f52a0eda093ff-probar-legal-services-senior-staff-attorney-tx-ca-american-bar-association-harlingen</t>
+  </si>
+  <si>
+    <t>Program and Operations Manager</t>
+  </si>
+  <si>
+    <t>University of Maryland - Philip Merrill College of Journalism</t>
+  </si>
+  <si>
+    <t>College Park, MD</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Media, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/187628f2c9414e79809074a8f5836e3a-program-and-operations-manager-university-of-maryland-philip-merrill-college-of-journalism-college-park</t>
+  </si>
+  <si>
+    <t>Program Associate, Partner Success (Full-Time Position, Hybrid)</t>
+  </si>
+  <si>
+    <t>Cause Strategy Partners</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/84de450ef6354073a47b2ef5fe326e9d-program-associate-partner-success-full-time-position-hybrid-cause-strategy-partners-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate, Reproductive Freedom Alliance</t>
+  </si>
+  <si>
+    <t>Governors Action Alliance</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Civic Engagement, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a7088563e354cce964d68a7104738fe-program-associate-reproductive-freedom-alliance-governors-action-alliance-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>The U District Partnership</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 81000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0e2add2789d4743a696f7cfde575562-program-coordinator-the-u-district-partnership-seattle</t>
+  </si>
+  <si>
+    <t>Jewish Community Relations Council of Greater Boston</t>
+  </si>
+  <si>
+    <t>Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f09580e9101449ba9bcb0470a9bb8955-program-coordinator-jewish-community-relations-council-of-greater-boston-boston</t>
+  </si>
+  <si>
+    <t>Program Coordinator (Full Time, Three-Year Term)</t>
+  </si>
+  <si>
+    <t>The Gilder Lehrman Institute of American History</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 63500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6d72385b61f4f0ba380910e3f18b86b-program-coordinator-full-time-three-year-term-the-gilder-lehrman-institute-of-american-history-new-york</t>
+  </si>
+  <si>
+    <t>Remote (Arkansas)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Economic Development</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69375f0c39f44c65b8a9cba6e2991b56-program-manager-southeastern-wind-coalition-raleigh</t>
+  </si>
+  <si>
     <t>Proposal Development Manager</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Part Time, Temporary</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/43b7272e709e433e9716141cdbc6a971-proposal-development-manager-welthungerhilfe-bonn</t>
   </si>
   <si>
+    <t>REAL ESTATE PROJECT MANAGER</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eed2803c950449378201088e03fbbe32-real-estate-project-manager-neighborworks-affiliates-boston</t>
+  </si>
+  <si>
+    <t>Recruiter</t>
+  </si>
+  <si>
+    <t>The Bronx Defenders</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1948e47f329442aaaa280ca834c95e04-recruiter-the-bronx-defenders-bronx</t>
+  </si>
+  <si>
     <t>Request for Proposals-Community -Led monitoring (CLM) Experts</t>
   </si>
   <si>
     <t>International Treatment Preparedness Coalition (ITPC)</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>Civic Engagement, Education, Health Medicine</t>
   </si>
   <si>
@@ -113,6 +1670,177 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/8c1f4d1b7d434d09a4bbc14a75059359-request-for-proposals-health-information-management-experts-international-treatment-preparedness-coalition-itpc-sandton</t>
+  </si>
+  <si>
+    <t>Risk and Loss Control Manager</t>
+  </si>
+  <si>
+    <t>The Captive Advantage</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/83dd43409c4a45f0b16a292a917650d7-risk-and-loss-control-manager-the-captive-advantage-boston</t>
+  </si>
+  <si>
+    <t>School Nurse Teacher</t>
+  </si>
+  <si>
+    <t>Providence Preparatory Charter School (PVD Prep)</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b60aaa26744e4db09cf55f20afac441a-school-nurse-teacher-providence-preparatory-charter-school-pvd-prep-providence</t>
+  </si>
+  <si>
+    <t>Senior Fightback Campaigner, Federal Advocacy</t>
+  </si>
+  <si>
+    <t>Popular Democracy</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/872bd172fbff42af8c2f55a3cee2cce0-senior-fightback-campaigner-federal-advocacy-popular-democracy-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager, Public Affairs</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f2b741623bf4b2fa306e26df4a2e74a-senior-manager-public-affairs-spoonfuls-newton</t>
+  </si>
+  <si>
+    <t>Senior Organizer or Organizing Manager</t>
+  </si>
+  <si>
+    <t>Detention Watch Network</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab8f11798a084e8eb83d15fd1006b48c-senior-organizer-or-organizing-manager-detention-watch-network-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of Puget Sound</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 24.04 - 26.44/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba2f110405dc4df5b9d6deca3fe8fb93-staff-accountant-big-brothers-big-sisters-of-puget-sound-bellevue</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Child Welfare Litigation</t>
+  </si>
+  <si>
+    <t>A Better Childhood</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd49881bb51a4491b04393ab68c41043-staff-attorney-child-welfare-litigation-a-better-childhood-new-york</t>
+  </si>
+  <si>
+    <t>Tech Youth Program Coordinator</t>
+  </si>
+  <si>
+    <t>Legacy International</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/740c328687e44235b29cef0e2f79f36a-tech-youth-program-coordinator-legacy-international-bedford</t>
+  </si>
+  <si>
+    <t>Vice President of Advancement</t>
+  </si>
+  <si>
+    <t>United Way of Erie County (PA)</t>
+  </si>
+  <si>
+    <t>Erie, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c73855e7018401d8a86447a9e48286c-vice-president-of-advancement-united-way-of-erie-county-pa-erie</t>
+  </si>
+  <si>
+    <t>Whole Family Housing Advocate</t>
+  </si>
+  <si>
+    <t>USD 23.65 - 23.65/hour</t>
+  </si>
+  <si>
+    <t>Research Social Science, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dfff421b106d46188213904a56c3da1c-whole-family-housing-advocate-champlain-valley-office-of-economic-opportunity-burlington</t>
+  </si>
+  <si>
+    <t>Writer/Editor for Animal Protection Nonprofit</t>
+  </si>
+  <si>
+    <t>Lady Freethinker</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Media, Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fa89eb7336249a0b829b17eb15eb2a3-writereditor-for-animal-protection-nonprofit-lady-freethinker-los-angeles</t>
+  </si>
+  <si>
+    <t>Youth Advocacy Initiative Coordinator</t>
+  </si>
+  <si>
+    <t>Safe Shores - The D.C. Children's Advocacy Center</t>
+  </si>
+  <si>
+    <t>USD 63630.00 - 63630.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a79f7476614b4ddab0188ecc907fec69-youth-advocacy-initiative-coordinator-safe-shores-the-dc-childrens-advocacy-center-washington</t>
+  </si>
+  <si>
+    <t>Youth Advocacy Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f40f65e00d94b55b1ee3b2020eda3f0-youth-advocacy-specialist-safe-shores-the-dc-childrens-advocacy-center-washington</t>
   </si>
 </sst>
 </file>
@@ -498,7 +2226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -537,8 +2265,778 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" t="s">
+        <v>164</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" t="s">
+        <v>170</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -546,7 +3044,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -585,8 +3083,61 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -594,7 +3145,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -635,117 +3186,1960 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>228</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>32</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" t="s">
+        <v>238</v>
+      </c>
+      <c r="F8" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" t="s">
+        <v>260</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" t="s">
+        <v>264</v>
+      </c>
+      <c r="F13" t="s">
+        <v>265</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" t="s">
+        <v>193</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C15" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" t="s">
+        <v>273</v>
+      </c>
+      <c r="F15" t="s">
+        <v>274</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" t="s">
+        <v>278</v>
+      </c>
+      <c r="F16" t="s">
+        <v>279</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>281</v>
+      </c>
+      <c r="B17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" t="s">
+        <v>286</v>
+      </c>
+      <c r="F18" t="s">
+        <v>287</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" t="s">
+        <v>290</v>
+      </c>
+      <c r="C19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" t="s">
+        <v>291</v>
+      </c>
+      <c r="E19" t="s">
+        <v>292</v>
+      </c>
+      <c r="F19" t="s">
+        <v>293</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>295</v>
+      </c>
+      <c r="B20" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" t="s">
+        <v>298</v>
+      </c>
+      <c r="F20" t="s">
+        <v>299</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>301</v>
+      </c>
+      <c r="B21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" t="s">
+        <v>304</v>
+      </c>
+      <c r="F21" t="s">
+        <v>305</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D22" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" t="s">
+        <v>310</v>
+      </c>
+      <c r="F22" t="s">
+        <v>311</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D23" t="s">
+        <v>215</v>
+      </c>
+      <c r="E23" t="s">
+        <v>315</v>
+      </c>
+      <c r="F23" t="s">
+        <v>316</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" t="s">
+        <v>215</v>
+      </c>
+      <c r="E24" t="s">
+        <v>321</v>
+      </c>
+      <c r="F24" t="s">
+        <v>322</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" t="s">
+        <v>237</v>
+      </c>
+      <c r="D25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" t="s">
+        <v>326</v>
+      </c>
+      <c r="F25" t="s">
+        <v>327</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26" t="s">
+        <v>304</v>
+      </c>
+      <c r="F26" t="s">
+        <v>222</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
+        <v>332</v>
+      </c>
+      <c r="C27" t="s">
+        <v>333</v>
+      </c>
+      <c r="D27" t="s">
+        <v>215</v>
+      </c>
+      <c r="E27" t="s">
+        <v>334</v>
+      </c>
+      <c r="F27" t="s">
+        <v>335</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>337</v>
+      </c>
+      <c r="B28" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" t="s">
+        <v>215</v>
+      </c>
+      <c r="E28" t="s">
+        <v>321</v>
+      </c>
+      <c r="F28" t="s">
+        <v>322</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B29" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" t="s">
+        <v>341</v>
+      </c>
+      <c r="D29" t="s">
+        <v>215</v>
+      </c>
+      <c r="E29" t="s">
+        <v>342</v>
+      </c>
+      <c r="F29" t="s">
+        <v>343</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B30" t="s">
+        <v>346</v>
+      </c>
+      <c r="C30" t="s">
+        <v>347</v>
+      </c>
+      <c r="D30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" t="s">
+        <v>348</v>
+      </c>
+      <c r="F30" t="s">
+        <v>349</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>351</v>
+      </c>
+      <c r="B31" t="s">
+        <v>352</v>
+      </c>
+      <c r="C31" t="s">
+        <v>353</v>
+      </c>
+      <c r="D31" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" t="s">
+        <v>354</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>356</v>
+      </c>
+      <c r="B32" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" t="s">
+        <v>353</v>
+      </c>
+      <c r="D32" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" t="s">
+        <v>354</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>358</v>
+      </c>
+      <c r="B33" t="s">
+        <v>359</v>
+      </c>
+      <c r="C33" t="s">
+        <v>360</v>
+      </c>
+      <c r="D33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E33" t="s">
+        <v>361</v>
+      </c>
+      <c r="F33" t="s">
+        <v>362</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>364</v>
+      </c>
+      <c r="B34" t="s">
+        <v>365</v>
+      </c>
+      <c r="C34" t="s">
+        <v>366</v>
+      </c>
+      <c r="D34" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" t="s">
+        <v>367</v>
+      </c>
+      <c r="F34" t="s">
+        <v>368</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>370</v>
+      </c>
+      <c r="B35" t="s">
+        <v>371</v>
+      </c>
+      <c r="C35" t="s">
+        <v>372</v>
+      </c>
+      <c r="D35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>370</v>
+      </c>
+      <c r="B36" t="s">
+        <v>374</v>
+      </c>
+      <c r="C36" t="s">
+        <v>375</v>
+      </c>
+      <c r="D36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" t="s">
+        <v>376</v>
+      </c>
+      <c r="F36" t="s">
+        <v>377</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>379</v>
+      </c>
+      <c r="B37" t="s">
+        <v>380</v>
+      </c>
+      <c r="C37" t="s">
+        <v>381</v>
+      </c>
+      <c r="D37" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" t="s">
+        <v>382</v>
+      </c>
+      <c r="F37" t="s">
+        <v>383</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>385</v>
+      </c>
+      <c r="B38" t="s">
+        <v>386</v>
+      </c>
+      <c r="C38" t="s">
+        <v>387</v>
+      </c>
+      <c r="D38" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" t="s">
+        <v>388</v>
+      </c>
+      <c r="F38" t="s">
+        <v>389</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>391</v>
+      </c>
+      <c r="B39" t="s">
+        <v>392</v>
+      </c>
+      <c r="C39" t="s">
+        <v>393</v>
+      </c>
+      <c r="D39" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" t="s">
+        <v>264</v>
+      </c>
+      <c r="F39" t="s">
+        <v>394</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>396</v>
+      </c>
+      <c r="B40" t="s">
+        <v>397</v>
+      </c>
+      <c r="C40" t="s">
+        <v>398</v>
+      </c>
+      <c r="D40" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" t="s">
+        <v>399</v>
+      </c>
+      <c r="F40" t="s">
+        <v>400</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>402</v>
+      </c>
+      <c r="B41" t="s">
+        <v>403</v>
+      </c>
+      <c r="C41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E41" t="s">
+        <v>404</v>
+      </c>
+      <c r="F41" t="s">
+        <v>405</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>407</v>
+      </c>
+      <c r="B42" t="s">
+        <v>408</v>
+      </c>
+      <c r="C42" t="s">
+        <v>409</v>
+      </c>
+      <c r="D42" t="s">
+        <v>410</v>
+      </c>
+      <c r="E42" t="s">
+        <v>193</v>
+      </c>
+      <c r="F42" t="s">
+        <v>411</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>413</v>
+      </c>
+      <c r="B43" t="s">
+        <v>414</v>
+      </c>
+      <c r="C43" t="s">
+        <v>415</v>
+      </c>
+      <c r="D43" t="s">
+        <v>215</v>
+      </c>
+      <c r="E43" t="s">
+        <v>416</v>
+      </c>
+      <c r="F43" t="s">
+        <v>417</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>419</v>
+      </c>
+      <c r="B44" t="s">
+        <v>420</v>
+      </c>
+      <c r="C44" t="s">
+        <v>421</v>
+      </c>
+      <c r="D44" t="s">
+        <v>215</v>
+      </c>
+      <c r="E44" t="s">
+        <v>422</v>
+      </c>
+      <c r="F44" t="s">
+        <v>423</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>425</v>
+      </c>
+      <c r="B45" t="s">
+        <v>426</v>
+      </c>
+      <c r="C45" t="s">
+        <v>427</v>
+      </c>
+      <c r="D45" t="s">
+        <v>215</v>
+      </c>
+      <c r="E45" t="s">
+        <v>428</v>
+      </c>
+      <c r="F45" t="s">
+        <v>429</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>431</v>
+      </c>
+      <c r="B46" t="s">
+        <v>432</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" t="s">
+        <v>215</v>
+      </c>
+      <c r="E46" t="s">
+        <v>193</v>
+      </c>
+      <c r="F46" t="s">
+        <v>433</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>435</v>
+      </c>
+      <c r="B47" t="s">
+        <v>436</v>
+      </c>
+      <c r="C47" t="s">
+        <v>242</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>437</v>
+      </c>
+      <c r="F47" t="s">
+        <v>438</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>440</v>
+      </c>
+      <c r="B48" t="s">
+        <v>426</v>
+      </c>
+      <c r="C48" t="s">
+        <v>427</v>
+      </c>
+      <c r="D48" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" t="s">
+        <v>441</v>
+      </c>
+      <c r="F48" t="s">
+        <v>429</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>443</v>
+      </c>
+      <c r="B49" t="s">
+        <v>444</v>
+      </c>
+      <c r="C49" t="s">
+        <v>445</v>
+      </c>
+      <c r="D49" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49" t="s">
+        <v>446</v>
+      </c>
+      <c r="F49" t="s">
+        <v>447</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>449</v>
+      </c>
+      <c r="B50" t="s">
+        <v>450</v>
+      </c>
+      <c r="C50" t="s">
+        <v>451</v>
+      </c>
+      <c r="D50" t="s">
+        <v>205</v>
+      </c>
+      <c r="E50" t="s">
+        <v>452</v>
+      </c>
+      <c r="F50" t="s">
+        <v>438</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>454</v>
+      </c>
+      <c r="B51" t="s">
+        <v>426</v>
+      </c>
+      <c r="C51" t="s">
+        <v>427</v>
+      </c>
+      <c r="D51" t="s">
+        <v>215</v>
+      </c>
+      <c r="E51" t="s">
+        <v>455</v>
+      </c>
+      <c r="F51" t="s">
+        <v>429</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>457</v>
+      </c>
+      <c r="B52" t="s">
+        <v>426</v>
+      </c>
+      <c r="C52" t="s">
+        <v>427</v>
+      </c>
+      <c r="D52" t="s">
+        <v>205</v>
+      </c>
+      <c r="E52" t="s">
+        <v>458</v>
+      </c>
+      <c r="F52" t="s">
+        <v>429</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>460</v>
+      </c>
+      <c r="B53" t="s">
+        <v>461</v>
+      </c>
+      <c r="C53" t="s">
+        <v>462</v>
+      </c>
+      <c r="D53" t="s">
+        <v>291</v>
+      </c>
+      <c r="E53" t="s">
+        <v>463</v>
+      </c>
+      <c r="F53" t="s">
+        <v>464</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>466</v>
+      </c>
+      <c r="B54" t="s">
+        <v>467</v>
+      </c>
+      <c r="C54" t="s">
+        <v>468</v>
+      </c>
+      <c r="D54" t="s">
+        <v>215</v>
+      </c>
+      <c r="E54" t="s">
+        <v>469</v>
+      </c>
+      <c r="F54" t="s">
+        <v>250</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>471</v>
+      </c>
+      <c r="B55" t="s">
+        <v>472</v>
+      </c>
+      <c r="C55" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" t="s">
+        <v>473</v>
+      </c>
+      <c r="F55" t="s">
+        <v>417</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>475</v>
+      </c>
+      <c r="B56" t="s">
+        <v>476</v>
+      </c>
+      <c r="C56" t="s">
+        <v>477</v>
+      </c>
+      <c r="D56" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56" t="s">
+        <v>478</v>
+      </c>
+      <c r="F56" t="s">
+        <v>479</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>481</v>
+      </c>
+      <c r="B57" t="s">
+        <v>263</v>
+      </c>
+      <c r="C57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D57" t="s">
+        <v>215</v>
+      </c>
+      <c r="E57" t="s">
+        <v>227</v>
+      </c>
+      <c r="F57" t="s">
+        <v>265</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>483</v>
+      </c>
+      <c r="B58" t="s">
+        <v>484</v>
+      </c>
+      <c r="C58" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" t="s">
+        <v>485</v>
+      </c>
+      <c r="F58" t="s">
+        <v>193</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>487</v>
+      </c>
+      <c r="B59" t="s">
+        <v>488</v>
+      </c>
+      <c r="C59" t="s">
+        <v>242</v>
+      </c>
+      <c r="D59" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" t="s">
+        <v>489</v>
+      </c>
+      <c r="F59" t="s">
+        <v>490</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>492</v>
+      </c>
+      <c r="B60" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" t="s">
+        <v>410</v>
+      </c>
+      <c r="E60" t="s">
+        <v>493</v>
+      </c>
+      <c r="F60" t="s">
+        <v>244</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>495</v>
+      </c>
+      <c r="B61" t="s">
+        <v>496</v>
+      </c>
+      <c r="C61" t="s">
+        <v>497</v>
+      </c>
+      <c r="D61" t="s">
+        <v>215</v>
+      </c>
+      <c r="E61" t="s">
+        <v>498</v>
+      </c>
+      <c r="F61" t="s">
+        <v>499</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>501</v>
+      </c>
+      <c r="B62" t="s">
+        <v>502</v>
+      </c>
+      <c r="C62" t="s">
+        <v>503</v>
+      </c>
+      <c r="D62" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" t="s">
+        <v>504</v>
+      </c>
+      <c r="F62" t="s">
+        <v>505</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>507</v>
+      </c>
+      <c r="B63" t="s">
+        <v>508</v>
+      </c>
+      <c r="C63" t="s">
+        <v>242</v>
+      </c>
+      <c r="D63" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" t="s">
+        <v>509</v>
+      </c>
+      <c r="F63" t="s">
+        <v>193</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>511</v>
+      </c>
+      <c r="B64" t="s">
+        <v>512</v>
+      </c>
+      <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="s">
+        <v>215</v>
+      </c>
+      <c r="E64" t="s">
+        <v>513</v>
+      </c>
+      <c r="F64" t="s">
+        <v>514</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>516</v>
+      </c>
+      <c r="B65" t="s">
+        <v>517</v>
+      </c>
+      <c r="C65" t="s">
+        <v>518</v>
+      </c>
+      <c r="D65" t="s">
+        <v>215</v>
+      </c>
+      <c r="E65" t="s">
+        <v>519</v>
+      </c>
+      <c r="F65" t="s">
+        <v>520</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>516</v>
+      </c>
+      <c r="B66" t="s">
+        <v>522</v>
+      </c>
+      <c r="C66" t="s">
+        <v>451</v>
+      </c>
+      <c r="D66" t="s">
+        <v>215</v>
+      </c>
+      <c r="E66" t="s">
+        <v>509</v>
+      </c>
+      <c r="F66" t="s">
+        <v>523</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>525</v>
+      </c>
+      <c r="B67" t="s">
+        <v>526</v>
+      </c>
+      <c r="C67" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" t="s">
+        <v>410</v>
+      </c>
+      <c r="E67" t="s">
+        <v>527</v>
+      </c>
+      <c r="F67" t="s">
+        <v>528</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" t="s">
+        <v>530</v>
+      </c>
+      <c r="D68" t="s">
+        <v>215</v>
+      </c>
+      <c r="E68" t="s">
+        <v>531</v>
+      </c>
+      <c r="F68" t="s">
+        <v>532</v>
+      </c>
+      <c r="G68" t="s">
+        <v>533</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>535</v>
+      </c>
+      <c r="B69" t="s">
+        <v>408</v>
+      </c>
+      <c r="C69" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" t="s">
+        <v>536</v>
+      </c>
+      <c r="E69" t="s">
+        <v>193</v>
+      </c>
+      <c r="F69" t="s">
+        <v>411</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>538</v>
+      </c>
+      <c r="B70" t="s">
+        <v>539</v>
+      </c>
+      <c r="C70" t="s">
+        <v>451</v>
+      </c>
+      <c r="D70" t="s">
+        <v>215</v>
+      </c>
+      <c r="E70" t="s">
+        <v>441</v>
+      </c>
+      <c r="F70" t="s">
+        <v>389</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>541</v>
+      </c>
+      <c r="B71" t="s">
+        <v>542</v>
+      </c>
+      <c r="C71" t="s">
+        <v>204</v>
+      </c>
+      <c r="D71" t="s">
+        <v>215</v>
+      </c>
+      <c r="E71" t="s">
+        <v>376</v>
+      </c>
+      <c r="F71" t="s">
+        <v>543</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>545</v>
+      </c>
+      <c r="B72" t="s">
+        <v>546</v>
+      </c>
+      <c r="C72" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" t="s">
+        <v>291</v>
+      </c>
+      <c r="E72" t="s">
+        <v>193</v>
+      </c>
+      <c r="F72" t="s">
+        <v>547</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>549</v>
+      </c>
+      <c r="B73" t="s">
+        <v>546</v>
+      </c>
+      <c r="C73" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" t="s">
+        <v>291</v>
+      </c>
+      <c r="E73" t="s">
+        <v>193</v>
+      </c>
+      <c r="F73" t="s">
+        <v>550</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>552</v>
+      </c>
+      <c r="B74" t="s">
+        <v>553</v>
+      </c>
+      <c r="C74" t="s">
+        <v>554</v>
+      </c>
+      <c r="D74" t="s">
+        <v>215</v>
+      </c>
+      <c r="E74" t="s">
+        <v>555</v>
+      </c>
+      <c r="F74" t="s">
+        <v>193</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>557</v>
+      </c>
+      <c r="B75" t="s">
+        <v>558</v>
+      </c>
+      <c r="C75" t="s">
+        <v>559</v>
+      </c>
+      <c r="D75" t="s">
+        <v>215</v>
+      </c>
+      <c r="E75" t="s">
+        <v>193</v>
+      </c>
+      <c r="F75" t="s">
+        <v>560</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>562</v>
+      </c>
+      <c r="B76" t="s">
+        <v>563</v>
+      </c>
+      <c r="C76" t="s">
+        <v>237</v>
+      </c>
+      <c r="D76" t="s">
+        <v>215</v>
+      </c>
+      <c r="E76" t="s">
+        <v>264</v>
+      </c>
+      <c r="F76" t="s">
+        <v>564</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>566</v>
+      </c>
+      <c r="B77" t="s">
+        <v>332</v>
+      </c>
+      <c r="C77" t="s">
+        <v>333</v>
+      </c>
+      <c r="D77" t="s">
+        <v>215</v>
+      </c>
+      <c r="E77" t="s">
+        <v>567</v>
+      </c>
+      <c r="F77" t="s">
+        <v>335</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>569</v>
+      </c>
+      <c r="B78" t="s">
+        <v>570</v>
+      </c>
+      <c r="C78" t="s">
+        <v>191</v>
+      </c>
+      <c r="D78" t="s">
+        <v>215</v>
+      </c>
+      <c r="E78" t="s">
+        <v>193</v>
+      </c>
+      <c r="F78" t="s">
+        <v>571</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>573</v>
+      </c>
+      <c r="B79" t="s">
+        <v>574</v>
+      </c>
+      <c r="C79" t="s">
+        <v>575</v>
+      </c>
+      <c r="D79" t="s">
+        <v>205</v>
+      </c>
+      <c r="E79" t="s">
+        <v>576</v>
+      </c>
+      <c r="F79" t="s">
+        <v>417</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>578</v>
+      </c>
+      <c r="B80" t="s">
+        <v>579</v>
+      </c>
+      <c r="C80" t="s">
+        <v>242</v>
+      </c>
+      <c r="D80" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" t="s">
+        <v>580</v>
+      </c>
+      <c r="F80" t="s">
+        <v>581</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>583</v>
+      </c>
+      <c r="B81" t="s">
+        <v>584</v>
+      </c>
+      <c r="C81" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" t="s">
+        <v>585</v>
+      </c>
+      <c r="F81" t="s">
+        <v>586</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>588</v>
+      </c>
+      <c r="B82" t="s">
+        <v>589</v>
+      </c>
+      <c r="C82" t="s">
+        <v>590</v>
+      </c>
+      <c r="D82" t="s">
+        <v>215</v>
+      </c>
+      <c r="E82" t="s">
+        <v>591</v>
+      </c>
+      <c r="F82" t="s">
+        <v>586</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>593</v>
+      </c>
+      <c r="B83" t="s">
+        <v>414</v>
+      </c>
+      <c r="C83" t="s">
+        <v>415</v>
+      </c>
+      <c r="D83" t="s">
+        <v>215</v>
+      </c>
+      <c r="E83" t="s">
+        <v>594</v>
+      </c>
+      <c r="F83" t="s">
+        <v>595</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>597</v>
+      </c>
+      <c r="B84" t="s">
+        <v>598</v>
+      </c>
+      <c r="C84" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" t="s">
+        <v>291</v>
+      </c>
+      <c r="E84" t="s">
+        <v>599</v>
+      </c>
+      <c r="F84" t="s">
+        <v>600</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>602</v>
+      </c>
+      <c r="B85" t="s">
+        <v>603</v>
+      </c>
+      <c r="C85" t="s">
+        <v>237</v>
+      </c>
+      <c r="D85" t="s">
+        <v>215</v>
+      </c>
+      <c r="E85" t="s">
+        <v>604</v>
+      </c>
+      <c r="F85" t="s">
+        <v>605</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>607</v>
+      </c>
+      <c r="B86" t="s">
+        <v>603</v>
+      </c>
+      <c r="C86" t="s">
+        <v>237</v>
+      </c>
+      <c r="D86" t="s">
+        <v>215</v>
+      </c>
+      <c r="E86" t="s">
+        <v>604</v>
+      </c>
+      <c r="F86" t="s">
+        <v>605</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -756,6 +5150,86 @@
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-06.xlsx
+++ b/docs/xlsx/jobs-2026-10-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="923">
   <si>
     <t>Title</t>
   </si>
@@ -643,6 +643,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/75276a6526a8429e93cbd71a2e201671-afterschool-coordinator-castle-hill-ymca-ymca-of-greater-new-york-bronx</t>
   </si>
   <si>
+    <t>Annual Giving Specialist (Association Office)</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7fc013329de4c0eb9dd9ca1690ac871-annual-giving-specialist-association-office-ymca-of-greater-new-york-new-york</t>
+  </si>
+  <si>
+    <t>AP Accountant</t>
+  </si>
+  <si>
+    <t>Futures Without Violence</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Women, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a780d5ead2a4546a5fce3f3343dbbae-ap-accountant-futures-without-violence-san-francisco</t>
+  </si>
+  <si>
     <t>Asistente de Redes Sociales Remoto/a</t>
   </si>
   <si>
@@ -661,9 +694,6 @@
     <t>ROC USA</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -673,6 +703,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/6cab186eeed14ed2a22da2b8d7b942ff-asset-manager-roc-usa-capital-roc-usa-washington</t>
   </si>
   <si>
+    <t>Assistant Controller</t>
+  </si>
+  <si>
+    <t>LifeMoves</t>
+  </si>
+  <si>
+    <t>Santa Clara, California</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffc0874e876d40cbb7f1678a48cf0277-assistant-controller-lifemoves-santa-clara</t>
+  </si>
+  <si>
     <t>Associate Director of Admissions</t>
   </si>
   <si>
@@ -724,6 +772,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4890b74e7a3343fca168d3c4e07fdb53-associate-director-foundation-giving-true-ground-housing-partners-arlington</t>
   </si>
   <si>
+    <t>Aunt Lute Books Co-Executive Director in Administration</t>
+  </si>
+  <si>
+    <t>aunt lute books</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 36000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Lgbtq, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0490ac5721c487388d8d6ffb691d532-aunt-lute-books-co-executive-director-in-administration-aunt-lute-books-san-francisco</t>
+  </si>
+  <si>
     <t>Chief Conservation Officer</t>
   </si>
   <si>
@@ -742,9 +808,6 @@
     <t>Innocence Project</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 229500.00 - 298000.00/year</t>
   </si>
   <si>
@@ -754,6 +817,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/d5ed5359f03248ca8a8fb1b39a0ac35d-chief-program-officer-exoneration-strategy-support-innocence-project-new-york</t>
   </si>
   <si>
+    <t>Child and Adolescent Forensic Interviewer</t>
+  </si>
+  <si>
+    <t>Safe Shores - The D.C. Children's Advocacy Center</t>
+  </si>
+  <si>
+    <t>USD 62800.00 - 62800.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3caf97a941074d6c845b5fec034dd46a-child-and-adolescent-forensic-interviewer-safe-shores-the-dc-childrens-advocacy-center-washington</t>
+  </si>
+  <si>
+    <t>Clinical Social Worker- Geriatric Mental Health</t>
+  </si>
+  <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 70040.00 - 73130.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85e32943496f486b8a0775989e5237d6-clinical-social-worker-geriatric-mental-health-jewish-association-serving-the-aging-bronx</t>
+  </si>
+  <si>
+    <t>Coach, Mindset</t>
+  </si>
+  <si>
+    <t>Episcopal Community Services</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/648777853b494465995917a46c1024bb-coach-mindset-episcopal-community-services-philadelphia</t>
+  </si>
+  <si>
     <t>Communications Manager, Start Early WA</t>
   </si>
   <si>
@@ -766,12 +874,27 @@
     <t>USD 73900.00 - 85000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/aaf8af60b41c4713bd046cf1c415396f-communications-manager-start-early-wa-start-early-chicago</t>
   </si>
   <si>
+    <t>Community Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Conservation Colorado</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bdb93ff28ae14d5995ea3364d9096042-community-fundraising-manager-conservation-colorado-denver</t>
+  </si>
+  <si>
     <t>Community Organizer, Hunts Point Community Partnership</t>
   </si>
   <si>
@@ -844,6 +967,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/793da77ec69f4f5f9f63a6be9ea2cc44-deputy-director-strategy-operations-the-nature-conservancy-conshohocken</t>
   </si>
   <si>
+    <t>Development &amp; Operations Associate</t>
+  </si>
+  <si>
+    <t>READ 718</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60aa9a6a8c7c464a92c4bb89f417e869-development-operations-associate-read-718-kings-county</t>
+  </si>
+  <si>
     <t>Whatcom Hills Waldorf School</t>
   </si>
   <si>
@@ -859,6 +1000,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/dea8746676104822a233e97505b880ec-development-director-whatcom-hills-waldorf-school-bellingham</t>
   </si>
   <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Resolve Philly</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89f0f4bf22464c62a2e4ec7ebb15e711-development-manager-resolve-philly-philadelphia</t>
+  </si>
+  <si>
     <t>Development Manager, Start Early WA</t>
   </si>
   <si>
@@ -988,6 +1144,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5c2088e7445542dab32a916256b08d46-director-of-jacj-cuisi-wildlife-sanctuary-comunidad-inti-wara-yassi-ciwy-san-buena-ventura-la-paz-bolivia</t>
   </si>
   <si>
+    <t>Director of Philanthropy</t>
+  </si>
+  <si>
+    <t>Free Law Project</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afc11b37b591440f9936c28d3215502b-director-of-philanthropy-free-law-project-oakland</t>
+  </si>
+  <si>
     <t>Director of Policy and Government Affairs</t>
   </si>
   <si>
@@ -1009,6 +1180,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/df931260942d408a8c00ec1911ae008b-director-of-program-admissions-impact-institute-for-nonprofit-practice-boston</t>
   </si>
   <si>
+    <t>Director of Renew Collaborative Expansion</t>
+  </si>
+  <si>
+    <t>HomeStart, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7163b432ebc944109e6c5e070c8f1c55-director-of-renew-collaborative-expansion-homestart-inc-boston</t>
+  </si>
+  <si>
     <t>Director, Corporate and Foundation Relations</t>
   </si>
   <si>
@@ -1171,6 +1357,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b8330b0a62ca476ca56cd9bf3496ac8e-executive-director-cambridge-center-for-adult-education-the-cambridge-center-for-adult-education-cambridge</t>
   </si>
   <si>
+    <t>Executive Director, Center for Safe Alaskans</t>
+  </si>
+  <si>
+    <t>The Foraker Group</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ee77c2dd6e54719b7123ea0b594a1c8-executive-director-center-for-safe-alaskans-the-foraker-group-anchorage</t>
+  </si>
+  <si>
     <t>Facilities Director</t>
   </si>
   <si>
@@ -1210,12 +1414,6 @@
     <t>Flatbush Cats</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
-    <t>USD 120000.00 - 140000.00/year</t>
-  </si>
-  <si>
     <t>Animals</t>
   </si>
   <si>
@@ -1237,6 +1435,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/2a75ef395a4747e6925b263ce94deb27-financial-coach-and-educator-just-a-start-cambridge</t>
   </si>
   <si>
+    <t>Gift Officer</t>
+  </si>
+  <si>
+    <t>Jewish Alliance for Law and Social Action (JALSA)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c05190ac205b46b2bf10324bd901a938-gift-officer-jewish-alliance-for-law-and-social-action-jalsa-boston</t>
+  </si>
+  <si>
+    <t>Grants Officer</t>
+  </si>
+  <si>
+    <t>Gordon and Betty Moore Foundation</t>
+  </si>
+  <si>
+    <t>Palo Alto, California</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cf93969f86e48208986a6f360f0846e-grants-officer-gordon-and-betty-moore-foundation-palo-alto</t>
+  </si>
+  <si>
     <t>Head of Project Sudan</t>
   </si>
   <si>
@@ -1267,9 +1498,6 @@
     <t>USD 23.73 - 28.76/hour</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/54b3c2246ae149e58dcd0ae6b5dcaefa-head-start-teacher-jj-flynn-elementary-champlain-valley-office-of-economic-opportunity-burlington</t>
   </si>
   <si>
@@ -1309,6 +1537,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/d3c94ed05d0f444bab83b87532299147-in-home-support-worker-hopewell-inc-dedham</t>
   </si>
   <si>
+    <t>Inclusion Concierge Program Specialist</t>
+  </si>
+  <si>
+    <t>The Kelsey</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efaea2d1bf8e4a6aa35d705ff39e2779-inclusion-concierge-program-specialist-the-kelsey-san-francisco</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05c1bc6c86c947ac9a836cf57c7017a8-inclusion-concierge-program-specialist-the-kelsey-san-jose</t>
+  </si>
+  <si>
     <t>Internal Communications Manager</t>
   </si>
   <si>
@@ -1321,6 +1570,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c01f20d4f4584cfb8351537e84baf210-internal-communications-manager-meliore-foundation-bruxelles</t>
   </si>
   <si>
+    <t>Investigator (Criminal Practice) - NDS Harlem</t>
+  </si>
+  <si>
+    <t>Neighborhood Defender Service of Harlem, New York</t>
+  </si>
+  <si>
+    <t>USD 68500.00 - 80650.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/221ad14d8ee04936b8e402599d2421dd-investigator-criminal-practice-nds-harlem-neighborhood-defender-service-of-harlem-new-york-new-york</t>
+  </si>
+  <si>
     <t>IT &amp; Office Associate</t>
   </si>
   <si>
@@ -1336,6 +1600,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/bc947aa95a99421fa228fc523067b28e-it-office-associate-writopia-lab-new-york</t>
   </si>
   <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN LA!</t>
+  </si>
+  <si>
+    <t>UNITE HERE! Local 11</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee159dffec694317a9cfc9a32d3b3c6c-join-a-progressive-campaign-in-la-unite-here-local-11-los-angeles</t>
+  </si>
+  <si>
+    <t>Junior Accountant</t>
+  </si>
+  <si>
+    <t>YWCA Princeton</t>
+  </si>
+  <si>
+    <t>Princeton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91f32f17e45f4a62a0fe1291ec801d32-junior-accountant-ywca-princeton-princeton</t>
+  </si>
+  <si>
     <t>Licensed Clinician-Worcester</t>
   </si>
   <si>
@@ -1369,9 +1669,6 @@
     <t>West End House</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 22.00 - 25.00/hour</t>
   </si>
   <si>
@@ -1414,6 +1711,33 @@
     <t>https://www.idealist.org/en/business-job/65a0b15d1dce45b0b382cbcec47b2439-local-food-access-delivery-driver-the-peoples-market-hyattsville</t>
   </si>
   <si>
+    <t>Manager of Program Operations: Focus on Educational Organization and Support to Multilingual ELLs</t>
+  </si>
+  <si>
+    <t>Bridges to Academic Success</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/486356efe29f475a8f72dadcbbe3ccac-manager-of-program-operations-focus-on-educational-organization-and-support-to-multilingual-ells-bridges-to-academic-success-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Finance and Accounting (US)</t>
+  </si>
+  <si>
+    <t>Regulatory Assistance Project</t>
+  </si>
+  <si>
+    <t>Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4728ccf0b5a4448998dbfb9dff29eaa9-manager-finance-and-accounting-us-regulatory-assistance-project-montpelier</t>
+  </si>
+  <si>
     <t>Manager, Office of the President</t>
   </si>
   <si>
@@ -1465,6 +1789,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/4ea097974a8d41b78dd6fb71072a7e75-nslp-operations-manager-metropolitan-council-on-jewish-poverty-new-york</t>
   </si>
   <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Pilsen Neighbors Community Council</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Civic Engagement, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a75d0716cc64233b8d53f26484d41ba-office-manager-pilsen-neighbors-community-council-chicago</t>
+  </si>
+  <si>
+    <t>Organizing Director</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7be200b3bd243f397a4cc330e16ac89-organizing-director-jewish-alliance-for-law-and-social-action-jalsa-boston</t>
+  </si>
+  <si>
     <t>Paralegal</t>
   </si>
   <si>
@@ -1492,6 +1840,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/bc1369ed198b4b6196a04384d5b55376-philanthropy-officer-the-breast-cancer-research-foundation-new-york</t>
   </si>
   <si>
+    <t>Phone Bank In Person for a Progressive Campaign!</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8595cd47849042e0b376ec358819efbc-phone-bank-in-person-for-a-progressive-campaign-unite-here-local-11-los-angeles</t>
+  </si>
+  <si>
     <t>Post-Conviction Litigation Fellow</t>
   </si>
   <si>
@@ -1501,6 +1858,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f6ddb3497f11463688baa52e4305f206-post-conviction-litigation-fellow-innocence-project-new-york</t>
   </si>
   <si>
+    <t>President/Senior Leader</t>
+  </si>
+  <si>
+    <t>CANCollaborate</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Health Medicine, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8945754cd70b4e7393a676637c8140e5-presidentsenior-leader-cancollaborate-great-falls</t>
+  </si>
+  <si>
     <t>ProBAR Legal Services - Senior Staff Attorney TX-CA</t>
   </si>
   <si>
@@ -1519,6 +1891,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/38b8b3a35ce8440cb40f52a0eda093ff-probar-legal-services-senior-staff-attorney-tx-ca-american-bar-association-harlingen</t>
   </si>
   <si>
+    <t>Procurement Coordinator</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37b53ff209ce4065b43ec3a4d969b2df-procurement-coordinator-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Program and Operations Manager</t>
   </si>
   <si>
@@ -1543,9 +1930,6 @@
     <t>Cause Strategy Partners</t>
   </si>
   <si>
-    <t>USD 55000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/business-job/84de450ef6354073a47b2ef5fe326e9d-program-associate-partner-success-full-time-position-hybrid-cause-strategy-partners-new-york</t>
   </si>
   <si>
@@ -1621,6 +2005,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/69375f0c39f44c65b8a9cba6e2991b56-program-manager-southeastern-wind-coalition-raleigh</t>
   </si>
   <si>
+    <t>Program Manager (Campus Partnerships)</t>
+  </si>
+  <si>
+    <t>Interfaith America</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/81cdc62dc2fa42679cd1c4d74e276f82-program-manager-campus-partnerships-interfaith-america-chicago</t>
+  </si>
+  <si>
     <t>Proposal Development Manager</t>
   </si>
   <si>
@@ -1735,6 +2131,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/ab8f11798a084e8eb83d15fd1006b48c-senior-organizer-or-organizing-manager-detention-watch-network-washington</t>
   </si>
   <si>
+    <t>Senior Policy and Analytics Manager – Medicaid Institute</t>
+  </si>
+  <si>
+    <t>United Hospital Fund of New York</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f8504ed8d0341b899f1dfc09bdab651-senior-policy-and-analytics-manager-medicaid-institute-united-hospital-fund-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Senior Software Engineer, Data Architecture</t>
+  </si>
+  <si>
+    <t>Outschool.org</t>
+  </si>
+  <si>
+    <t>USD 60.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7227ee4a3ea4dbaabb8f6ab7c73e816-senior-software-engineer-data-architecture-outschoolorg-san-francisco</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
@@ -1750,6 +2176,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/ba2f110405dc4df5b9d6deca3fe8fb93-staff-accountant-big-brothers-big-sisters-of-puget-sound-bellevue</t>
   </si>
   <si>
+    <t>Staff Attorney – Full-Time or Part-Time</t>
+  </si>
+  <si>
+    <t>Veterans Law Center</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb9a3167ba6546b9ae476921a66ca460-staff-attorney-full-time-or-part-time-veterans-law-center-philadelphia</t>
+  </si>
+  <si>
     <t>Staff Attorney, Child Welfare Litigation</t>
   </si>
   <si>
@@ -1765,6 +2206,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/bd49881bb51a4491b04393ab68c41043-staff-attorney-child-welfare-litigation-a-better-childhood-new-york</t>
   </si>
   <si>
+    <t>Staff Attorney/Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Prison Law Office</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 134055.00 - 265903.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c113f18b7304fe092e20fbe3206d67f-staff-attorneysenior-staff-attorney-prison-law-office-berkeley</t>
+  </si>
+  <si>
+    <t>State Policy Manager</t>
+  </si>
+  <si>
+    <t>Afterschool Alliance</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0fcf18f9c9043c3877065441e506d7b-state-policy-manager-afterschool-alliance-washington</t>
+  </si>
+  <si>
     <t>Tech Youth Program Coordinator</t>
   </si>
   <si>
@@ -1795,6 +2266,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/9c73855e7018401d8a86447a9e48286c-vice-president-of-advancement-united-way-of-erie-county-pa-erie</t>
   </si>
   <si>
+    <t>Vice President of Fundraising</t>
+  </si>
+  <si>
+    <t>Book Trust</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/097c5ffaa83a4a96a1d74b4a1979c817-vice-president-of-fundraising-book-trust-denver</t>
+  </si>
+  <si>
     <t>Whole Family Housing Advocate</t>
   </si>
   <si>
@@ -1825,15 +2308,9 @@
     <t>Youth Advocacy Initiative Coordinator</t>
   </si>
   <si>
-    <t>Safe Shores - The D.C. Children's Advocacy Center</t>
-  </si>
-  <si>
     <t>USD 63630.00 - 63630.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Mental Health, Victim Support</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/a79f7476614b4ddab0188ecc907fec69-youth-advocacy-initiative-coordinator-safe-shores-the-dc-childrens-advocacy-center-washington</t>
   </si>
   <si>
@@ -1841,6 +2318,471 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/7f40f65e00d94b55b1ee3b2020eda3f0-youth-advocacy-specialist-safe-shores-the-dc-childrens-advocacy-center-washington</t>
+  </si>
+  <si>
+    <t>ADMINISTRATION AND FINANCE ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Field and Fork Network</t>
+  </si>
+  <si>
+    <t>Buffalo, New York</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73774263</t>
+  </si>
+  <si>
+    <t>ASSOCIATE EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>New Roots Institute</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73797481</t>
+  </si>
+  <si>
+    <t>CACFP PROGRAM SPECIALIST</t>
+  </si>
+  <si>
+    <t>Childrens Hunger Alliance</t>
+  </si>
+  <si>
+    <t>Toledo, Ohio</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73818255</t>
+  </si>
+  <si>
+    <t>CAMPAIGN SPECIALIST</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73798703</t>
+  </si>
+  <si>
+    <t>CHIEF OF STAFF</t>
+  </si>
+  <si>
+    <t>Fairer Fields</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73795037</t>
+  </si>
+  <si>
+    <t>CO-DIRECTOR</t>
+  </si>
+  <si>
+    <t>Farm School NYC</t>
+  </si>
+  <si>
+    <t>Hyrbid in New York, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73817033</t>
+  </si>
+  <si>
+    <t>COMMUNITY ENGAGEMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>PINE MEADOW RANCH CENTER FOR ARTS AND AGRICULTURE - The Roundhouse Foundation</t>
+  </si>
+  <si>
+    <t>Sisters, Oregon</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73807257</t>
+  </si>
+  <si>
+    <t>COMMUNITY MARKET ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Crossroads</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73790149</t>
+  </si>
+  <si>
+    <t>COMMUNITY OUTREACH MANAGER</t>
+  </si>
+  <si>
+    <t>UNITED STATES - World Central Kitchen</t>
+  </si>
+  <si>
+    <t>Preferred Location(s): West, Central &amp; South. Must</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73809701</t>
+  </si>
+  <si>
+    <t>CULINARY DIRECTOR</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73792593</t>
+  </si>
+  <si>
+    <t>DAIRY PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73781595</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT MANAGER</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73775485</t>
+  </si>
+  <si>
+    <t>DIGITAL COMMUNICATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>Farm Action</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73780373</t>
+  </si>
+  <si>
+    <t>DIRECTOR GENERAL</t>
+  </si>
+  <si>
+    <t>AQUATIC AND CROP RESOURCE DEVELOPMENT - National Research Council Canada</t>
+  </si>
+  <si>
+    <t>Halifax, Nova Scotia</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73815811</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF AGRICULTURE</t>
+  </si>
+  <si>
+    <t>Cedar Circle Farm and Education Center</t>
+  </si>
+  <si>
+    <t>East Thetford, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73770597</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF FOUNDATION RELATIONS</t>
+  </si>
+  <si>
+    <t>Food and Water Watch</t>
+  </si>
+  <si>
+    <t>Remote or choice of in-person location in Washingt</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73768153</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF INVESTMENTS</t>
+  </si>
+  <si>
+    <t>Proofing Station</t>
+  </si>
+  <si>
+    <t>Remote in the Upper Midwest, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73786483</t>
+  </si>
+  <si>
+    <t>DOUBLE UP FOOD BUCKS PROGRAM AMBASSADOR WEST MICHIGAN</t>
+  </si>
+  <si>
+    <t>Fair Food Network</t>
+  </si>
+  <si>
+    <t>Grand Rapids, West Michigan, Michigan</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73785261</t>
+  </si>
+  <si>
+    <t>EDUCATION COORDINATOR â€“ CENTRAL TEXAS</t>
+  </si>
+  <si>
+    <t>Sustainable Food Center</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73793815</t>
+  </si>
+  <si>
+    <t>EMERGING ISSUES SPECIALIST</t>
+  </si>
+  <si>
+    <t>LIMITED SERVICE - Vermont Department of Agriculture Food and Markets Agency</t>
+  </si>
+  <si>
+    <t>Williston, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73776707</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Compost Research and Education Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73799925</t>
+  </si>
+  <si>
+    <t>FARM COORDINATOR</t>
+  </si>
+  <si>
+    <t>DAIRY SPECIALIST - Growing Gardens</t>
+  </si>
+  <si>
+    <t>Boulder, Colorado</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73765709</t>
+  </si>
+  <si>
+    <t>FARM EDUCATION AND VOLUNTEER COORDINATOR</t>
+  </si>
+  <si>
+    <t>Redeemer Valley Farm</t>
+  </si>
+  <si>
+    <t>Huntingdon Valley, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73773041</t>
+  </si>
+  <si>
+    <t>FARM MANAGER</t>
+  </si>
+  <si>
+    <t>MEVO</t>
+  </si>
+  <si>
+    <t>Mahwah, New Jersey</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73777929</t>
+  </si>
+  <si>
+    <t>GRANT PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>The Roundhouse Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73808479</t>
+  </si>
+  <si>
+    <t>ILLINOIS AGRICULTURAL AND CONSERVATION TECHNICAL SPECIALIST</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Effingham, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73802369</t>
+  </si>
+  <si>
+    <t>INVESTMENT READINESS PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73787705</t>
+  </si>
+  <si>
+    <t>LEAD</t>
+  </si>
+  <si>
+    <t>REGENERATIVE AGRICULTURE - PUR</t>
+  </si>
+  <si>
+    <t>Toronto, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73814589</t>
+  </si>
+  <si>
+    <t>PART TIME DESIGN INTERN</t>
+  </si>
+  <si>
+    <t>Building Impact Through Eaters</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73813367</t>
+  </si>
+  <si>
+    <t>PART-TIME BOOKKEEPER</t>
+  </si>
+  <si>
+    <t>Firsthand Foods</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73801147</t>
+  </si>
+  <si>
+    <t>PRIVATE LANDS BIOLOGIST</t>
+  </si>
+  <si>
+    <t>Ducks Unlimited</t>
+  </si>
+  <si>
+    <t>Richmond, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73804813</t>
+  </si>
+  <si>
+    <t>PRODUCER SUPPORT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Growing GRASS</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73779151</t>
+  </si>
+  <si>
+    <t>PROGRAM AMBASSADOR GENESEE COUNTY</t>
+  </si>
+  <si>
+    <t>Genesee County, Michigan</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73782817</t>
+  </si>
+  <si>
+    <t>PROGRAM EVALUATION SPECIALIST</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73769375</t>
+  </si>
+  <si>
+    <t>REGIONAL ALTERNATIVE INVESTMENT MANAGER AND FINANCE ASSISTANT</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73806035</t>
+  </si>
+  <si>
+    <t>RESEARCH FELLOW â€” MANAGED HONEY BEES</t>
+  </si>
+  <si>
+    <t>Remote, with preference for Washington DC, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73796259</t>
+  </si>
+  <si>
+    <t>SALES REPRESENTATIVE</t>
+  </si>
+  <si>
+    <t>ACCOUNT MANAGEMENT - Creekside Organics</t>
+  </si>
+  <si>
+    <t>Bakersfield, California</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73810923</t>
+  </si>
+  <si>
+    <t>KEY ACCOUNTS - Creekside Organics</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73812145</t>
+  </si>
+  <si>
+    <t>SENIOR COMMUNITY MARKET MANAGER â€“ NUTRITION PHARMACY</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73788927</t>
+  </si>
+  <si>
+    <t>SENIOR MANAGER</t>
+  </si>
+  <si>
+    <t>NUTRITION PRESCRIPTION INITIATIVES - Capital Area Food Bank</t>
+  </si>
+  <si>
+    <t>Washington DC Area, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73771819</t>
+  </si>
+  <si>
+    <t>SUSTAINABILITY PROGRAM SPECIALIST</t>
+  </si>
+  <si>
+    <t>Innovative Ag Services</t>
+  </si>
+  <si>
+    <t>Central City, Iowa</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73803591</t>
+  </si>
+  <si>
+    <t>TECHNOLOGY COORDINATOR</t>
+  </si>
+  <si>
+    <t>NASS PROGRAM - National Association of State Departments of Agriculture</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73766931</t>
+  </si>
+  <si>
+    <t>VALUE CHAIN SPECIALIST</t>
+  </si>
+  <si>
+    <t>Hybrid with travel in Michigan, Michigan</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73784039</t>
+  </si>
+  <si>
+    <t>WAREHOUSE ASSOCIATE</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73791371</t>
   </si>
 </sst>
 </file>
@@ -3145,7 +4087,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3212,62 +4154,62 @@
         <v>209</v>
       </c>
       <c r="B3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" t="s">
         <v>210</v>
       </c>
-      <c r="C3" t="s">
-        <v>191</v>
-      </c>
       <c r="D3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
         <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="F5" t="s">
         <v>222</v>
@@ -3284,62 +4226,62 @@
         <v>225</v>
       </c>
       <c r="C6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" t="s">
         <v>226</v>
       </c>
-      <c r="D6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>227</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" t="s">
         <v>230</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>231</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" t="s">
         <v>232</v>
       </c>
-      <c r="D7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>233</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" t="s">
         <v>236</v>
       </c>
-      <c r="B8" t="s">
-        <v>129</v>
-      </c>
       <c r="C8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E8" t="s">
         <v>237</v>
       </c>
-      <c r="D8" t="s">
-        <v>215</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>238</v>
-      </c>
-      <c r="F8" t="s">
-        <v>193</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>239</v>
@@ -3356,7 +4298,7 @@
         <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
         <v>243</v>
@@ -3379,7 +4321,7 @@
         <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
         <v>249</v>
@@ -3399,39 +4341,39 @@
         <v>253</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="D11" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F12" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>261</v>
@@ -3445,10 +4387,10 @@
         <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E13" t="s">
         <v>264</v>
@@ -3468,631 +4410,631 @@
         <v>268</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>270</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F15" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F16" t="s">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="D17" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E17" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F17" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B18" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>289</v>
       </c>
       <c r="D18" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F18" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>291</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F19" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B20" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C20" t="s">
-        <v>297</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B21" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C21" t="s">
-        <v>303</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C22" t="s">
-        <v>309</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E22" t="s">
+        <v>305</v>
+      </c>
+      <c r="F22" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="F22" t="s">
-        <v>311</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>311</v>
+      </c>
+      <c r="B23" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" t="s">
         <v>313</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>211</v>
+      </c>
+      <c r="E23" t="s">
         <v>314</v>
       </c>
-      <c r="C23" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" t="s">
-        <v>215</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>315</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>317</v>
+      </c>
+      <c r="B24" t="s">
         <v>318</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>319</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" t="s">
         <v>320</v>
       </c>
-      <c r="D24" t="s">
-        <v>215</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>321</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" t="s">
         <v>324</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
+        <v>211</v>
+      </c>
+      <c r="E25" t="s">
         <v>325</v>
       </c>
-      <c r="C25" t="s">
-        <v>237</v>
-      </c>
-      <c r="D25" t="s">
-        <v>215</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>326</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" t="s">
         <v>329</v>
       </c>
-      <c r="B26" t="s">
-        <v>220</v>
-      </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="D26" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E26" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="F26" t="s">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B27" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="C27" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="D27" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E27" t="s">
         <v>334</v>
       </c>
       <c r="F27" t="s">
+        <v>233</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>336</v>
+      </c>
+      <c r="B28" t="s">
         <v>337</v>
       </c>
-      <c r="B28" t="s">
-        <v>319</v>
-      </c>
       <c r="C28" t="s">
-        <v>320</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E28" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="F28" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C29" t="s">
-        <v>341</v>
+        <v>191</v>
       </c>
       <c r="D29" t="s">
-        <v>215</v>
+        <v>343</v>
       </c>
       <c r="E29" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F29" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B30" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D30" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E30" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F30" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B31" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D31" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>356</v>
       </c>
       <c r="F31" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B32" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C32" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D32" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E32" t="s">
-        <v>193</v>
+        <v>362</v>
       </c>
       <c r="F32" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C33" t="s">
-        <v>360</v>
+        <v>191</v>
       </c>
       <c r="D33" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E33" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F33" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B34" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="C34" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D34" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="F34" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C35" t="s">
-        <v>372</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>378</v>
       </c>
       <c r="F35" t="s">
-        <v>193</v>
+        <v>379</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C36" t="s">
-        <v>375</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E36" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F36" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="C37" t="s">
-        <v>381</v>
+        <v>191</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E37" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="F37" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B38" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C38" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E38" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F38" t="s">
-        <v>389</v>
+        <v>250</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C39" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D39" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E39" t="s">
-        <v>264</v>
+        <v>396</v>
       </c>
       <c r="F39" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="C40" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="D40" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E40" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="F40" t="s">
+        <v>374</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>401</v>
+      </c>
+      <c r="B41" t="s">
         <v>402</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>403</v>
       </c>
-      <c r="C41" t="s">
-        <v>381</v>
-      </c>
       <c r="D41" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E41" t="s">
         <v>404</v>
@@ -4115,10 +5057,10 @@
         <v>409</v>
       </c>
       <c r="D42" t="s">
+        <v>211</v>
+      </c>
+      <c r="E42" t="s">
         <v>410</v>
-      </c>
-      <c r="E42" t="s">
-        <v>193</v>
       </c>
       <c r="F42" t="s">
         <v>411</v>
@@ -4138,1008 +5080,1790 @@
         <v>415</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
+        <v>193</v>
+      </c>
+      <c r="F43" t="s">
         <v>416</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>418</v>
+      </c>
+      <c r="B44" t="s">
+        <v>414</v>
+      </c>
+      <c r="C44" t="s">
+        <v>415</v>
+      </c>
+      <c r="D44" t="s">
+        <v>211</v>
+      </c>
+      <c r="E44" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" t="s">
+        <v>416</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="B44" t="s">
-        <v>420</v>
-      </c>
-      <c r="C44" t="s">
-        <v>421</v>
-      </c>
-      <c r="D44" t="s">
-        <v>215</v>
-      </c>
-      <c r="E44" t="s">
-        <v>422</v>
-      </c>
-      <c r="F44" t="s">
-        <v>423</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>420</v>
+      </c>
+      <c r="B45" t="s">
+        <v>421</v>
+      </c>
+      <c r="C45" t="s">
+        <v>422</v>
+      </c>
+      <c r="D45" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" t="s">
+        <v>423</v>
+      </c>
+      <c r="F45" t="s">
+        <v>424</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B45" t="s">
-        <v>426</v>
-      </c>
-      <c r="C45" t="s">
-        <v>427</v>
-      </c>
-      <c r="D45" t="s">
-        <v>215</v>
-      </c>
-      <c r="E45" t="s">
-        <v>428</v>
-      </c>
-      <c r="F45" t="s">
-        <v>429</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>426</v>
+      </c>
+      <c r="B46" t="s">
+        <v>427</v>
+      </c>
+      <c r="C46" t="s">
+        <v>428</v>
+      </c>
+      <c r="D46" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" t="s">
+        <v>429</v>
+      </c>
+      <c r="F46" t="s">
+        <v>430</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="B46" t="s">
-        <v>432</v>
-      </c>
-      <c r="C46" t="s">
-        <v>191</v>
-      </c>
-      <c r="D46" t="s">
-        <v>215</v>
-      </c>
-      <c r="E46" t="s">
-        <v>193</v>
-      </c>
-      <c r="F46" t="s">
-        <v>433</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>432</v>
+      </c>
+      <c r="B47" t="s">
+        <v>433</v>
+      </c>
+      <c r="C47" t="s">
+        <v>434</v>
+      </c>
+      <c r="D47" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" t="s">
+        <v>193</v>
+      </c>
+      <c r="F47" t="s">
+        <v>193</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="B47" t="s">
-        <v>436</v>
-      </c>
-      <c r="C47" t="s">
-        <v>242</v>
-      </c>
-      <c r="D47" t="s">
-        <v>215</v>
-      </c>
-      <c r="E47" t="s">
-        <v>437</v>
-      </c>
-      <c r="F47" t="s">
-        <v>438</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>432</v>
+      </c>
+      <c r="B48" t="s">
+        <v>436</v>
+      </c>
+      <c r="C48" t="s">
+        <v>437</v>
+      </c>
+      <c r="D48" t="s">
+        <v>211</v>
+      </c>
+      <c r="E48" t="s">
+        <v>438</v>
+      </c>
+      <c r="F48" t="s">
+        <v>439</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="B48" t="s">
-        <v>426</v>
-      </c>
-      <c r="C48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D48" t="s">
-        <v>215</v>
-      </c>
-      <c r="E48" t="s">
-        <v>441</v>
-      </c>
-      <c r="F48" t="s">
-        <v>429</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>441</v>
+      </c>
+      <c r="B49" t="s">
+        <v>442</v>
+      </c>
+      <c r="C49" t="s">
         <v>443</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
+        <v>211</v>
+      </c>
+      <c r="E49" t="s">
         <v>444</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
         <v>445</v>
       </c>
-      <c r="D49" t="s">
-        <v>215</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="H49" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="F49" t="s">
-        <v>447</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>447</v>
+      </c>
+      <c r="B50" t="s">
+        <v>448</v>
+      </c>
+      <c r="C50" t="s">
         <v>449</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
+        <v>211</v>
+      </c>
+      <c r="E50" t="s">
         <v>450</v>
       </c>
-      <c r="C50" t="s">
+      <c r="F50" t="s">
         <v>451</v>
       </c>
-      <c r="D50" t="s">
-        <v>205</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="H50" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="F50" t="s">
-        <v>438</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>453</v>
+      </c>
+      <c r="B51" t="s">
         <v>454</v>
       </c>
-      <c r="B51" t="s">
-        <v>426</v>
-      </c>
       <c r="C51" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E51" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F51" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="C52" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E52" t="s">
-        <v>458</v>
+        <v>305</v>
       </c>
       <c r="F52" t="s">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C53" t="s">
-        <v>462</v>
+        <v>319</v>
       </c>
       <c r="D53" t="s">
-        <v>291</v>
+        <v>211</v>
       </c>
       <c r="E53" t="s">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="F53" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C54" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="D54" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E54" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F54" t="s">
-        <v>250</v>
+        <v>471</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C55" t="s">
-        <v>237</v>
+        <v>475</v>
       </c>
       <c r="D55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E55" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="F55" t="s">
-        <v>417</v>
+        <v>476</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B56" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C56" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D56" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F56" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s">
-        <v>263</v>
+        <v>485</v>
       </c>
       <c r="C57" t="s">
-        <v>242</v>
+        <v>486</v>
       </c>
       <c r="D57" t="s">
-        <v>215</v>
+        <v>487</v>
       </c>
       <c r="E57" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="F57" t="s">
-        <v>265</v>
+        <v>488</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B58" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C58" t="s">
-        <v>242</v>
+        <v>492</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E58" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F58" t="s">
-        <v>193</v>
+        <v>321</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B59" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C59" t="s">
-        <v>242</v>
+        <v>497</v>
       </c>
       <c r="D59" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E59" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="F59" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s">
-        <v>241</v>
+        <v>502</v>
       </c>
       <c r="C60" t="s">
-        <v>242</v>
+        <v>503</v>
       </c>
       <c r="D60" t="s">
-        <v>410</v>
+        <v>211</v>
       </c>
       <c r="E60" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F60" t="s">
-        <v>244</v>
+        <v>505</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C61" t="s">
-        <v>497</v>
+        <v>216</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E61" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="F61" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B62" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C62" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E62" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F62" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C63" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="D63" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E63" t="s">
-        <v>509</v>
+        <v>193</v>
       </c>
       <c r="F63" t="s">
-        <v>193</v>
+        <v>516</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B64" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C64" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D64" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E64" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="F64" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B65" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C65" t="s">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="D65" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E65" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F65" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B66" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C66" t="s">
-        <v>451</v>
+        <v>530</v>
       </c>
       <c r="D66" t="s">
-        <v>215</v>
+        <v>487</v>
       </c>
       <c r="E66" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="F66" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="B67" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="C67" t="s">
-        <v>242</v>
+        <v>536</v>
       </c>
       <c r="D67" t="s">
-        <v>410</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="F67" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>189</v>
+        <v>540</v>
       </c>
       <c r="B68" t="s">
-        <v>190</v>
+        <v>502</v>
       </c>
       <c r="C68" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="D68" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E68" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="F68" t="s">
-        <v>532</v>
-      </c>
-      <c r="G68" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B69" t="s">
-        <v>408</v>
+        <v>544</v>
       </c>
       <c r="C69" t="s">
-        <v>191</v>
+        <v>545</v>
       </c>
       <c r="D69" t="s">
-        <v>536</v>
+        <v>211</v>
       </c>
       <c r="E69" t="s">
-        <v>193</v>
+        <v>546</v>
       </c>
       <c r="F69" t="s">
-        <v>411</v>
+        <v>547</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B70" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="C70" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="D70" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E70" t="s">
-        <v>441</v>
+        <v>551</v>
       </c>
       <c r="F70" t="s">
-        <v>389</v>
+        <v>526</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="B71" t="s">
-        <v>542</v>
+        <v>502</v>
       </c>
       <c r="C71" t="s">
-        <v>204</v>
+        <v>503</v>
       </c>
       <c r="D71" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
-        <v>376</v>
+        <v>554</v>
       </c>
       <c r="F71" t="s">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B72" t="s">
-        <v>546</v>
+        <v>502</v>
       </c>
       <c r="C72" t="s">
-        <v>191</v>
+        <v>503</v>
       </c>
       <c r="D72" t="s">
-        <v>291</v>
+        <v>205</v>
       </c>
       <c r="E72" t="s">
-        <v>193</v>
+        <v>557</v>
       </c>
       <c r="F72" t="s">
-        <v>547</v>
+        <v>505</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B73" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>561</v>
       </c>
       <c r="D73" t="s">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="E73" t="s">
-        <v>193</v>
+        <v>562</v>
       </c>
       <c r="F73" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="C74" t="s">
-        <v>554</v>
+        <v>210</v>
       </c>
       <c r="D74" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E74" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="F74" t="s">
-        <v>193</v>
+        <v>568</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="B75" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C75" t="s">
-        <v>559</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E75" t="s">
-        <v>193</v>
+        <v>438</v>
       </c>
       <c r="F75" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="B76" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C76" t="s">
-        <v>237</v>
+        <v>576</v>
       </c>
       <c r="D76" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
-        <v>264</v>
+        <v>577</v>
       </c>
       <c r="F76" t="s">
-        <v>564</v>
+        <v>233</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="B77" t="s">
-        <v>332</v>
+        <v>580</v>
       </c>
       <c r="C77" t="s">
-        <v>333</v>
+        <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E77" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="F77" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B78" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="C78" t="s">
-        <v>191</v>
+        <v>585</v>
       </c>
       <c r="D78" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E78" t="s">
-        <v>193</v>
+        <v>586</v>
       </c>
       <c r="F78" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="B79" t="s">
-        <v>574</v>
+        <v>304</v>
       </c>
       <c r="C79" t="s">
-        <v>575</v>
+        <v>210</v>
       </c>
       <c r="D79" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E79" t="s">
-        <v>576</v>
+        <v>243</v>
       </c>
       <c r="F79" t="s">
-        <v>417</v>
+        <v>306</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="B80" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="C80" t="s">
-        <v>242</v>
+        <v>593</v>
       </c>
       <c r="D80" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E80" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="F80" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="B81" t="s">
-        <v>584</v>
+        <v>474</v>
       </c>
       <c r="C81" t="s">
-        <v>191</v>
+        <v>475</v>
       </c>
       <c r="D81" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>585</v>
+        <v>193</v>
       </c>
       <c r="F81" t="s">
-        <v>586</v>
+        <v>476</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="B82" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="C82" t="s">
-        <v>590</v>
+        <v>210</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="F82" t="s">
-        <v>586</v>
+        <v>193</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="B83" t="s">
-        <v>414</v>
+        <v>604</v>
       </c>
       <c r="C83" t="s">
-        <v>415</v>
+        <v>210</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="F83" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B84" t="s">
-        <v>598</v>
+        <v>529</v>
       </c>
       <c r="C84" t="s">
-        <v>191</v>
+        <v>530</v>
       </c>
       <c r="D84" t="s">
-        <v>291</v>
+        <v>487</v>
       </c>
       <c r="E84" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="F84" t="s">
-        <v>600</v>
+        <v>532</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="B85" t="s">
-        <v>603</v>
+        <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="D85" t="s">
-        <v>215</v>
+        <v>487</v>
       </c>
       <c r="E85" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="F85" t="s">
-        <v>605</v>
+        <v>265</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B86" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C86" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D86" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E86" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="F86" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>608</v>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>619</v>
+      </c>
+      <c r="B87" t="s">
+        <v>620</v>
+      </c>
+      <c r="C87" t="s">
+        <v>621</v>
+      </c>
+      <c r="D87" t="s">
+        <v>211</v>
+      </c>
+      <c r="E87" t="s">
+        <v>622</v>
+      </c>
+      <c r="F87" t="s">
+        <v>623</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>625</v>
+      </c>
+      <c r="B88" t="s">
+        <v>626</v>
+      </c>
+      <c r="C88" t="s">
+        <v>530</v>
+      </c>
+      <c r="D88" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" t="s">
+        <v>627</v>
+      </c>
+      <c r="F88" t="s">
+        <v>628</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>630</v>
+      </c>
+      <c r="B89" t="s">
+        <v>631</v>
+      </c>
+      <c r="C89" t="s">
+        <v>632</v>
+      </c>
+      <c r="D89" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" t="s">
+        <v>633</v>
+      </c>
+      <c r="F89" t="s">
+        <v>634</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>636</v>
+      </c>
+      <c r="B90" t="s">
+        <v>637</v>
+      </c>
+      <c r="C90" t="s">
+        <v>210</v>
+      </c>
+      <c r="D90" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" t="s">
+        <v>567</v>
+      </c>
+      <c r="F90" t="s">
+        <v>193</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>639</v>
+      </c>
+      <c r="B91" t="s">
+        <v>640</v>
+      </c>
+      <c r="C91" t="s">
+        <v>191</v>
+      </c>
+      <c r="D91" t="s">
+        <v>211</v>
+      </c>
+      <c r="E91" t="s">
+        <v>641</v>
+      </c>
+      <c r="F91" t="s">
+        <v>642</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>644</v>
+      </c>
+      <c r="B92" t="s">
+        <v>645</v>
+      </c>
+      <c r="C92" t="s">
+        <v>646</v>
+      </c>
+      <c r="D92" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" t="s">
+        <v>647</v>
+      </c>
+      <c r="F92" t="s">
+        <v>648</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>644</v>
+      </c>
+      <c r="B93" t="s">
+        <v>650</v>
+      </c>
+      <c r="C93" t="s">
+        <v>475</v>
+      </c>
+      <c r="D93" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93" t="s">
+        <v>567</v>
+      </c>
+      <c r="F93" t="s">
+        <v>651</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>653</v>
+      </c>
+      <c r="B94" t="s">
+        <v>654</v>
+      </c>
+      <c r="C94" t="s">
+        <v>210</v>
+      </c>
+      <c r="D94" t="s">
+        <v>487</v>
+      </c>
+      <c r="E94" t="s">
+        <v>655</v>
+      </c>
+      <c r="F94" t="s">
+        <v>656</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>189</v>
+      </c>
+      <c r="B95" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" t="s">
+        <v>658</v>
+      </c>
+      <c r="D95" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" t="s">
+        <v>659</v>
+      </c>
+      <c r="F95" t="s">
+        <v>660</v>
+      </c>
+      <c r="G95" t="s">
+        <v>661</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>663</v>
+      </c>
+      <c r="B96" t="s">
+        <v>664</v>
+      </c>
+      <c r="C96" t="s">
+        <v>593</v>
+      </c>
+      <c r="D96" t="s">
+        <v>211</v>
+      </c>
+      <c r="E96" t="s">
+        <v>641</v>
+      </c>
+      <c r="F96" t="s">
+        <v>665</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>667</v>
+      </c>
+      <c r="B97" t="s">
+        <v>485</v>
+      </c>
+      <c r="C97" t="s">
+        <v>191</v>
+      </c>
+      <c r="D97" t="s">
+        <v>668</v>
+      </c>
+      <c r="E97" t="s">
+        <v>193</v>
+      </c>
+      <c r="F97" t="s">
+        <v>488</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>670</v>
+      </c>
+      <c r="B98" t="s">
+        <v>671</v>
+      </c>
+      <c r="C98" t="s">
+        <v>475</v>
+      </c>
+      <c r="D98" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" t="s">
+        <v>541</v>
+      </c>
+      <c r="F98" t="s">
+        <v>457</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>673</v>
+      </c>
+      <c r="B99" t="s">
+        <v>674</v>
+      </c>
+      <c r="C99" t="s">
+        <v>204</v>
+      </c>
+      <c r="D99" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" t="s">
+        <v>438</v>
+      </c>
+      <c r="F99" t="s">
+        <v>675</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>677</v>
+      </c>
+      <c r="B100" t="s">
+        <v>678</v>
+      </c>
+      <c r="C100" t="s">
+        <v>191</v>
+      </c>
+      <c r="D100" t="s">
+        <v>343</v>
+      </c>
+      <c r="E100" t="s">
+        <v>193</v>
+      </c>
+      <c r="F100" t="s">
+        <v>679</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>681</v>
+      </c>
+      <c r="B101" t="s">
+        <v>678</v>
+      </c>
+      <c r="C101" t="s">
+        <v>191</v>
+      </c>
+      <c r="D101" t="s">
+        <v>343</v>
+      </c>
+      <c r="E101" t="s">
+        <v>193</v>
+      </c>
+      <c r="F101" t="s">
+        <v>682</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>684</v>
+      </c>
+      <c r="B102" t="s">
+        <v>685</v>
+      </c>
+      <c r="C102" t="s">
+        <v>686</v>
+      </c>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" t="s">
+        <v>687</v>
+      </c>
+      <c r="F102" t="s">
+        <v>193</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>689</v>
+      </c>
+      <c r="B103" t="s">
+        <v>690</v>
+      </c>
+      <c r="C103" t="s">
+        <v>691</v>
+      </c>
+      <c r="D103" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103" t="s">
+        <v>193</v>
+      </c>
+      <c r="F103" t="s">
+        <v>692</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>694</v>
+      </c>
+      <c r="B104" t="s">
+        <v>695</v>
+      </c>
+      <c r="C104" t="s">
+        <v>259</v>
+      </c>
+      <c r="D104" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104" t="s">
+        <v>305</v>
+      </c>
+      <c r="F104" t="s">
+        <v>696</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>698</v>
+      </c>
+      <c r="B105" t="s">
+        <v>394</v>
+      </c>
+      <c r="C105" t="s">
+        <v>395</v>
+      </c>
+      <c r="D105" t="s">
+        <v>211</v>
+      </c>
+      <c r="E105" t="s">
+        <v>699</v>
+      </c>
+      <c r="F105" t="s">
+        <v>397</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>701</v>
+      </c>
+      <c r="B106" t="s">
+        <v>702</v>
+      </c>
+      <c r="C106" t="s">
+        <v>191</v>
+      </c>
+      <c r="D106" t="s">
+        <v>211</v>
+      </c>
+      <c r="E106" t="s">
+        <v>193</v>
+      </c>
+      <c r="F106" t="s">
+        <v>703</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>705</v>
+      </c>
+      <c r="B107" t="s">
+        <v>706</v>
+      </c>
+      <c r="C107" t="s">
+        <v>210</v>
+      </c>
+      <c r="D107" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107" t="s">
+        <v>707</v>
+      </c>
+      <c r="F107" t="s">
+        <v>708</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>710</v>
+      </c>
+      <c r="B108" t="s">
+        <v>711</v>
+      </c>
+      <c r="C108" t="s">
+        <v>191</v>
+      </c>
+      <c r="D108" t="s">
+        <v>343</v>
+      </c>
+      <c r="E108" t="s">
+        <v>712</v>
+      </c>
+      <c r="F108" t="s">
+        <v>713</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>715</v>
+      </c>
+      <c r="B109" t="s">
+        <v>716</v>
+      </c>
+      <c r="C109" t="s">
+        <v>717</v>
+      </c>
+      <c r="D109" t="s">
+        <v>205</v>
+      </c>
+      <c r="E109" t="s">
+        <v>718</v>
+      </c>
+      <c r="F109" t="s">
+        <v>321</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>720</v>
+      </c>
+      <c r="B110" t="s">
+        <v>721</v>
+      </c>
+      <c r="C110" t="s">
+        <v>279</v>
+      </c>
+      <c r="D110" t="s">
+        <v>205</v>
+      </c>
+      <c r="E110" t="s">
+        <v>722</v>
+      </c>
+      <c r="F110" t="s">
+        <v>723</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>725</v>
+      </c>
+      <c r="B111" t="s">
+        <v>726</v>
+      </c>
+      <c r="C111" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" t="s">
+        <v>211</v>
+      </c>
+      <c r="E111" t="s">
+        <v>727</v>
+      </c>
+      <c r="F111" t="s">
+        <v>728</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>730</v>
+      </c>
+      <c r="B112" t="s">
+        <v>731</v>
+      </c>
+      <c r="C112" t="s">
+        <v>732</v>
+      </c>
+      <c r="D112" t="s">
+        <v>211</v>
+      </c>
+      <c r="E112" t="s">
+        <v>733</v>
+      </c>
+      <c r="F112" t="s">
+        <v>734</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>736</v>
+      </c>
+      <c r="B113" t="s">
+        <v>737</v>
+      </c>
+      <c r="C113" t="s">
+        <v>259</v>
+      </c>
+      <c r="D113" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" t="s">
+        <v>541</v>
+      </c>
+      <c r="F113" t="s">
+        <v>738</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>740</v>
+      </c>
+      <c r="B114" t="s">
+        <v>741</v>
+      </c>
+      <c r="C114" t="s">
+        <v>191</v>
+      </c>
+      <c r="D114" t="s">
+        <v>211</v>
+      </c>
+      <c r="E114" t="s">
+        <v>742</v>
+      </c>
+      <c r="F114" t="s">
+        <v>743</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>745</v>
+      </c>
+      <c r="B115" t="s">
+        <v>746</v>
+      </c>
+      <c r="C115" t="s">
+        <v>747</v>
+      </c>
+      <c r="D115" t="s">
+        <v>211</v>
+      </c>
+      <c r="E115" t="s">
+        <v>748</v>
+      </c>
+      <c r="F115" t="s">
+        <v>743</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>750</v>
+      </c>
+      <c r="B116" t="s">
+        <v>751</v>
+      </c>
+      <c r="C116" t="s">
+        <v>191</v>
+      </c>
+      <c r="D116" t="s">
+        <v>211</v>
+      </c>
+      <c r="E116" t="s">
+        <v>752</v>
+      </c>
+      <c r="F116" t="s">
+        <v>321</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>754</v>
+      </c>
+      <c r="B117" t="s">
+        <v>491</v>
+      </c>
+      <c r="C117" t="s">
+        <v>492</v>
+      </c>
+      <c r="D117" t="s">
+        <v>211</v>
+      </c>
+      <c r="E117" t="s">
+        <v>755</v>
+      </c>
+      <c r="F117" t="s">
+        <v>756</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>758</v>
+      </c>
+      <c r="B118" t="s">
+        <v>759</v>
+      </c>
+      <c r="C118" t="s">
+        <v>191</v>
+      </c>
+      <c r="D118" t="s">
+        <v>343</v>
+      </c>
+      <c r="E118" t="s">
+        <v>760</v>
+      </c>
+      <c r="F118" t="s">
+        <v>761</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>763</v>
+      </c>
+      <c r="B119" t="s">
+        <v>268</v>
+      </c>
+      <c r="C119" t="s">
+        <v>259</v>
+      </c>
+      <c r="D119" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" t="s">
+        <v>764</v>
+      </c>
+      <c r="F119" t="s">
+        <v>270</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>766</v>
+      </c>
+      <c r="B120" t="s">
+        <v>268</v>
+      </c>
+      <c r="C120" t="s">
+        <v>259</v>
+      </c>
+      <c r="D120" t="s">
+        <v>211</v>
+      </c>
+      <c r="E120" t="s">
+        <v>764</v>
+      </c>
+      <c r="F120" t="s">
+        <v>270</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>767</v>
       </c>
     </row>
   </sheetData>
@@ -5230,6 +6954,40 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5238,7 +6996,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5277,8 +7035,1066 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>768</v>
+      </c>
+      <c r="B2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
+        <v>771</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B3" t="s">
+        <v>774</v>
+      </c>
+      <c r="C3" t="s">
+        <v>775</v>
+      </c>
+      <c r="D3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" t="s">
+        <v>771</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>777</v>
+      </c>
+      <c r="B4" t="s">
+        <v>778</v>
+      </c>
+      <c r="C4" t="s">
+        <v>779</v>
+      </c>
+      <c r="D4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" t="s">
+        <v>780</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B5" t="s">
+        <v>774</v>
+      </c>
+      <c r="C5" t="s">
+        <v>775</v>
+      </c>
+      <c r="D5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
+        <v>783</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>785</v>
+      </c>
+      <c r="B6" t="s">
+        <v>786</v>
+      </c>
+      <c r="C6" t="s">
+        <v>787</v>
+      </c>
+      <c r="D6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" t="s">
+        <v>432</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>789</v>
+      </c>
+      <c r="B7" t="s">
+        <v>790</v>
+      </c>
+      <c r="C7" t="s">
+        <v>791</v>
+      </c>
+      <c r="D7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" t="s">
+        <v>432</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>793</v>
+      </c>
+      <c r="B8" t="s">
+        <v>794</v>
+      </c>
+      <c r="C8" t="s">
+        <v>795</v>
+      </c>
+      <c r="D8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" t="s">
+        <v>796</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>798</v>
+      </c>
+      <c r="B9" t="s">
+        <v>799</v>
+      </c>
+      <c r="C9" t="s">
+        <v>800</v>
+      </c>
+      <c r="D9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" t="s">
+        <v>780</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>802</v>
+      </c>
+      <c r="B10" t="s">
+        <v>803</v>
+      </c>
+      <c r="C10" t="s">
+        <v>804</v>
+      </c>
+      <c r="D10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" t="s">
+        <v>780</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>806</v>
+      </c>
+      <c r="B11" t="s">
+        <v>799</v>
+      </c>
+      <c r="C11" t="s">
+        <v>800</v>
+      </c>
+      <c r="D11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" t="s">
+        <v>780</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>808</v>
+      </c>
+      <c r="B12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C12" t="s">
+        <v>775</v>
+      </c>
+      <c r="D12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" t="s">
+        <v>809</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>811</v>
+      </c>
+      <c r="B13" t="s">
+        <v>769</v>
+      </c>
+      <c r="C13" t="s">
+        <v>770</v>
+      </c>
+      <c r="D13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" t="s">
+        <v>812</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>814</v>
+      </c>
+      <c r="B14" t="s">
+        <v>815</v>
+      </c>
+      <c r="C14" t="s">
+        <v>775</v>
+      </c>
+      <c r="D14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" t="s">
+        <v>796</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>817</v>
+      </c>
+      <c r="B15" t="s">
+        <v>818</v>
+      </c>
+      <c r="C15" t="s">
+        <v>819</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" t="s">
+        <v>820</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>822</v>
+      </c>
+      <c r="B16" t="s">
+        <v>823</v>
+      </c>
+      <c r="C16" t="s">
+        <v>824</v>
+      </c>
+      <c r="D16" t="s">
+        <v>193</v>
+      </c>
+      <c r="E16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16" t="s">
+        <v>780</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>826</v>
+      </c>
+      <c r="B17" t="s">
+        <v>827</v>
+      </c>
+      <c r="C17" t="s">
+        <v>828</v>
+      </c>
+      <c r="D17" t="s">
+        <v>193</v>
+      </c>
+      <c r="E17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F17" t="s">
+        <v>812</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>830</v>
+      </c>
+      <c r="B18" t="s">
+        <v>831</v>
+      </c>
+      <c r="C18" t="s">
+        <v>832</v>
+      </c>
+      <c r="D18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" t="s">
+        <v>812</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>834</v>
+      </c>
+      <c r="B19" t="s">
+        <v>835</v>
+      </c>
+      <c r="C19" t="s">
+        <v>836</v>
+      </c>
+      <c r="D19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F19" t="s">
+        <v>780</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>838</v>
+      </c>
+      <c r="B20" t="s">
+        <v>839</v>
+      </c>
+      <c r="C20" t="s">
+        <v>840</v>
+      </c>
+      <c r="D20" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F20" t="s">
+        <v>780</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>842</v>
+      </c>
+      <c r="B21" t="s">
+        <v>843</v>
+      </c>
+      <c r="C21" t="s">
+        <v>844</v>
+      </c>
+      <c r="D21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" t="s">
+        <v>780</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>846</v>
+      </c>
+      <c r="B22" t="s">
+        <v>847</v>
+      </c>
+      <c r="C22" t="s">
+        <v>775</v>
+      </c>
+      <c r="D22" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" t="s">
+        <v>432</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>849</v>
+      </c>
+      <c r="B23" t="s">
+        <v>850</v>
+      </c>
+      <c r="C23" t="s">
+        <v>851</v>
+      </c>
+      <c r="D23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" t="s">
+        <v>780</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>853</v>
+      </c>
+      <c r="B24" t="s">
+        <v>854</v>
+      </c>
+      <c r="C24" t="s">
+        <v>855</v>
+      </c>
+      <c r="D24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" t="s">
+        <v>193</v>
+      </c>
+      <c r="F24" t="s">
+        <v>780</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>857</v>
+      </c>
+      <c r="B25" t="s">
+        <v>858</v>
+      </c>
+      <c r="C25" t="s">
+        <v>859</v>
+      </c>
+      <c r="D25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" t="s">
+        <v>780</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>861</v>
+      </c>
+      <c r="B26" t="s">
+        <v>862</v>
+      </c>
+      <c r="C26" t="s">
+        <v>795</v>
+      </c>
+      <c r="D26" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" t="s">
+        <v>771</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>864</v>
+      </c>
+      <c r="B27" t="s">
+        <v>865</v>
+      </c>
+      <c r="C27" t="s">
+        <v>866</v>
+      </c>
+      <c r="D27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" t="s">
+        <v>780</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>868</v>
+      </c>
+      <c r="B28" t="s">
+        <v>831</v>
+      </c>
+      <c r="C28" t="s">
+        <v>832</v>
+      </c>
+      <c r="D28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" t="s">
+        <v>193</v>
+      </c>
+      <c r="F28" t="s">
+        <v>780</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>870</v>
+      </c>
+      <c r="B29" t="s">
+        <v>871</v>
+      </c>
+      <c r="C29" t="s">
+        <v>872</v>
+      </c>
+      <c r="D29" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" t="s">
+        <v>780</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>874</v>
+      </c>
+      <c r="B30" t="s">
+        <v>875</v>
+      </c>
+      <c r="C30" t="s">
+        <v>775</v>
+      </c>
+      <c r="D30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" t="s">
+        <v>193</v>
+      </c>
+      <c r="F30" t="s">
+        <v>796</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>877</v>
+      </c>
+      <c r="B31" t="s">
+        <v>878</v>
+      </c>
+      <c r="C31" t="s">
+        <v>403</v>
+      </c>
+      <c r="D31" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" t="s">
+        <v>771</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>880</v>
+      </c>
+      <c r="B32" t="s">
+        <v>881</v>
+      </c>
+      <c r="C32" t="s">
+        <v>882</v>
+      </c>
+      <c r="D32" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" t="s">
+        <v>820</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>884</v>
+      </c>
+      <c r="B33" t="s">
+        <v>885</v>
+      </c>
+      <c r="C33" t="s">
+        <v>775</v>
+      </c>
+      <c r="D33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E33" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" t="s">
+        <v>809</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>887</v>
+      </c>
+      <c r="B34" t="s">
+        <v>835</v>
+      </c>
+      <c r="C34" t="s">
+        <v>888</v>
+      </c>
+      <c r="D34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" t="s">
+        <v>780</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>890</v>
+      </c>
+      <c r="B35" t="s">
+        <v>865</v>
+      </c>
+      <c r="C35" t="s">
+        <v>775</v>
+      </c>
+      <c r="D35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" t="s">
+        <v>820</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>892</v>
+      </c>
+      <c r="B36" t="s">
+        <v>862</v>
+      </c>
+      <c r="C36" t="s">
+        <v>795</v>
+      </c>
+      <c r="D36" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" t="s">
+        <v>193</v>
+      </c>
+      <c r="F36" t="s">
+        <v>771</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>894</v>
+      </c>
+      <c r="B37" t="s">
+        <v>786</v>
+      </c>
+      <c r="C37" t="s">
+        <v>895</v>
+      </c>
+      <c r="D37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E37" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" t="s">
+        <v>820</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>897</v>
+      </c>
+      <c r="B38" t="s">
+        <v>898</v>
+      </c>
+      <c r="C38" t="s">
+        <v>899</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
+        <v>193</v>
+      </c>
+      <c r="F38" t="s">
+        <v>900</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>897</v>
+      </c>
+      <c r="B39" t="s">
+        <v>902</v>
+      </c>
+      <c r="C39" t="s">
+        <v>899</v>
+      </c>
+      <c r="D39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" t="s">
+        <v>193</v>
+      </c>
+      <c r="F39" t="s">
+        <v>900</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>904</v>
+      </c>
+      <c r="B40" t="s">
+        <v>799</v>
+      </c>
+      <c r="C40" t="s">
+        <v>800</v>
+      </c>
+      <c r="D40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" t="s">
+        <v>193</v>
+      </c>
+      <c r="F40" t="s">
+        <v>780</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>906</v>
+      </c>
+      <c r="B41" t="s">
+        <v>907</v>
+      </c>
+      <c r="C41" t="s">
+        <v>908</v>
+      </c>
+      <c r="D41" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" t="s">
+        <v>193</v>
+      </c>
+      <c r="F41" t="s">
+        <v>780</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>910</v>
+      </c>
+      <c r="B42" t="s">
+        <v>911</v>
+      </c>
+      <c r="C42" t="s">
+        <v>912</v>
+      </c>
+      <c r="D42" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" t="s">
+        <v>193</v>
+      </c>
+      <c r="F42" t="s">
+        <v>780</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>914</v>
+      </c>
+      <c r="B43" t="s">
+        <v>915</v>
+      </c>
+      <c r="C43" t="s">
+        <v>248</v>
+      </c>
+      <c r="D43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E43" t="s">
+        <v>193</v>
+      </c>
+      <c r="F43" t="s">
+        <v>916</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>918</v>
+      </c>
+      <c r="B44" t="s">
+        <v>835</v>
+      </c>
+      <c r="C44" t="s">
+        <v>919</v>
+      </c>
+      <c r="D44" t="s">
+        <v>193</v>
+      </c>
+      <c r="E44" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" t="s">
+        <v>780</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>921</v>
+      </c>
+      <c r="B45" t="s">
+        <v>799</v>
+      </c>
+      <c r="C45" t="s">
+        <v>800</v>
+      </c>
+      <c r="D45" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" t="s">
+        <v>193</v>
+      </c>
+      <c r="F45" t="s">
+        <v>780</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>922</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
